--- a/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>44</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2017</v>
+        <v>2720</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1659</v>
+        <v>2209</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>389</v>
+        <v>610</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>233</v>
+        <v>326</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>341</v>
+        <v>435</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>72</v>
+        <v>142</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>176</v>
+        <v>252</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>352</v>
+        <v>494</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>219</v>
+        <v>288</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>291</v>
+        <v>368</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>178</v>
+        <v>226</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>249</v>
+        <v>326</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -910,12 +910,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>07171</t>
+          <t>17131</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CIVITAVECCHIA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -929,47 +929,47 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>138</v>
+        <v>193</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>121</v>
+        <v>214</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>100</v>
+        <v>153</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>154</v>
+        <v>388</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>8</v>
+        <v>345</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>17131</t>
+          <t>07171</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CIVITAVECCHIA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -983,35 +983,35 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>130</v>
+        <v>173</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>277</v>
+        <v>211</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>245</v>
+        <v>17</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1037,31 +1037,31 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>114</v>
+        <v>156</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>145</v>
+        <v>204</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>107</v>
+        <v>157</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>134</v>
+        <v>178</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>154</v>
+        <v>198</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,31 +1145,31 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="G17" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="H17" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>107</v>
+      </c>
+      <c r="J17" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="K17" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L17" s="12" t="n">
+        <v>189</v>
+      </c>
+      <c r="M17" s="12" t="n">
         <v>9</v>
-      </c>
-      <c r="H17" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="I17" s="12" t="n">
-        <v>85</v>
-      </c>
-      <c r="J17" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="K17" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L17" s="12" t="n">
-        <v>144</v>
-      </c>
-      <c r="M17" s="12" t="n">
-        <v>8</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1199,28 +1199,28 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>3</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>43</v>
@@ -1234,17 +1234,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>06905</t>
+          <t>07473</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>RIETI</t>
+          <t>MONTEFIASCONE</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Scagnetti Giampiero</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1253,52 +1253,52 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="F19" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="H19" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="G19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="I19" s="12" t="n">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>07473</t>
+          <t>06905</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>MONTEFIASCONE</t>
+          <t>RIETI</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Scagnetti Giampiero</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1307,85 +1307,85 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="G20" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="J20" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="K20" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="H20" s="12" t="n">
-        <v>58</v>
-      </c>
-      <c r="I20" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="J20" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="K20" s="12" t="n">
-        <v>7</v>
-      </c>
       <c r="L20" s="12" t="n">
+        <v>77</v>
+      </c>
+      <c r="M20" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="M20" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>56322</t>
+          <t>16968</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>FIUMICINO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Manzo Fabio</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>159</v>
+        <v>85</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>80008</t>
+          <t>56322</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1406,40 +1406,40 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Manzo Fabio</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>64</v>
+        <v>171</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>148</v>
+        <v>206</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1450,12 +1450,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>16968</t>
+          <t>80008</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>FIUMICINO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,35 +1465,35 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>58</v>
+        <v>193</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1523,28 +1523,28 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>4</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>158</v>
+        <v>220</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
@@ -1558,7 +1558,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>17111</t>
+          <t>07221</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1577,47 +1577,47 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>27224</t>
+          <t>17111</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>CAMPAGNANO DI ROMA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,35 +1627,35 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>69</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H26" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="I26" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="F26" s="12" t="n">
-        <v>57</v>
-      </c>
-      <c r="G26" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="I26" s="12" t="n">
-        <v>23</v>
-      </c>
       <c r="J26" s="12" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>32</v>
+        <v>117</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>07221</t>
+          <t>57176</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1674,150 +1674,146 @@
           <t>ROMA</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+      <c r="C27" s="2" t="inlineStr"/>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>54638</t>
+          <t>27224</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>VITERBO</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr"/>
+          <t>CAMPAGNANO DI ROMA</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>07132</t>
+          <t>54638</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>MARINO</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Manzo Fabio</t>
-        </is>
-      </c>
+          <t>VITERBO</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr"/>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>11</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1843,82 +1839,82 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="H30" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="I30" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="J30" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="G30" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="H30" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="I30" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="J30" s="12" t="n">
-        <v>20</v>
-      </c>
       <c r="K30" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>59331</t>
+          <t>07132</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>MONTALTO DI CASTRO</t>
+          <t>MARINO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Manzo Fabio</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
@@ -1951,28 +1947,28 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>3</v>
@@ -1986,46 +1982,50 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>57176</t>
+          <t>59331</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr"/>
+          <t>MONTALTO DI CASTRO</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J33" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="K33" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K33" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="L33" s="12" t="n">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>36953</t>
+          <t>58258</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2055,42 +2055,42 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>55307</t>
+          <t>36953</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2105,35 +2105,35 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>43</v>
+        <v>134</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2144,50 +2144,50 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>58258</t>
+          <t>36942</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CASTEL GANDOLFO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Manzo Fabio</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I36" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="F36" s="12" t="n">
-        <v>57</v>
-      </c>
-      <c r="G36" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H36" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="I36" s="12" t="n">
-        <v>16</v>
-      </c>
       <c r="J36" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K36" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="K36" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="L36" s="12" t="n">
-        <v>89</v>
+        <v>36</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>58342</t>
+          <t>07143</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2208,40 +2208,40 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Manzo Fabio</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F37" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="G37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I37" s="12" t="n">
-        <v>19</v>
-      </c>
       <c r="J37" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>27100</t>
+          <t>58342</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2267,35 +2267,35 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J38" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K38" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K38" s="12" t="n">
+      <c r="L38" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="M38" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="L38" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="M38" s="12" t="n">
-        <v>22</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>07143</t>
+          <t>55307</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2316,91 +2316,91 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Manzo Fabio</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="J39" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K39" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H39" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="J39" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K39" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="L39" s="12" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>55811</t>
+          <t>58351</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>POMEZIA</t>
+          <t>VALMONTONE</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Funari Emanuele</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="M40" s="12" t="n">
         <v>0</v>
@@ -2414,50 +2414,50 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>36942</t>
+          <t>55811</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>CASTEL GANDOLFO</t>
+          <t>POMEZIA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Manzo Fabio</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J41" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -2468,50 +2468,50 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>58351</t>
+          <t>27100</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>VALMONTONE</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Funari Emanuele</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -2541,28 +2541,28 @@
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>3</v>
@@ -2595,31 +2595,31 @@
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
@@ -2649,139 +2649,135 @@
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="M45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>57171</t>
+          <t>07084</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>LADISPOLI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Scagnetti Giampiero</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="M46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>07164</t>
+          <t>59309</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>CASTEL GANDOLFO</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+          <t>MORLUPO</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr"/>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
@@ -2792,104 +2788,108 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>07084</t>
+          <t>57171</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>LADISPOLI</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Scagnetti Giampiero</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="M48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>59309</t>
+          <t>07164</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>MORLUPO</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr"/>
+          <t>CASTEL GANDOLFO</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J49" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J49" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="K49" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F50" s="12" t="n">
         <v>0</v>
@@ -2923,7 +2923,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J50" s="12" t="n">
         <v>2</v>
@@ -2932,14 +2932,14 @@
         <v>0</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F51" s="12" t="n">
         <v>0</v>
@@ -2973,7 +2973,7 @@
         <v>0</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J51" s="12" t="n">
         <v>0</v>
@@ -2982,14 +2982,14 @@
         <v>3</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3018,13 +3018,13 @@
         <v>2</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I52" s="12" t="n">
         <v>2</v>
@@ -3068,13 +3068,13 @@
         <v>0</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="G53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I53" s="12" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
         <v>0</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G54" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -845,7 +845,7 @@
         <v>494</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.1417004048582996</v>
+        <v>70</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>326</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.3128834355828221</v>
+        <v>102</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>388</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.8891752577319587</v>
+        <v>345</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>211</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.08056872037914692</v>
+        <v>17</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>157</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>0.03821656050955414</v>
+        <v>6</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>198</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.005050505050505051</v>
+        <v>1</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>189</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.04761904761904762</v>
+        <v>9</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>117</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.3675213675213675</v>
+        <v>43</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>29</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.2413793103448276</v>
+        <v>7</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>77</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.2987012987012987</v>
+        <v>23</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>206</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.1067961165048544</v>
+        <v>22</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>193</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.02072538860103627</v>
+        <v>4</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>119</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.04201680672268908</v>
+        <v>5</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>117</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0.03418803418803419</v>
+        <v>4</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>44</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.2045454545454546</v>
+        <v>9</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>35</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>0.6285714285714286</v>
+        <v>22</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>30</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>134</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>0.01492537313432836</v>
+        <v>2</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
         <v>36</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>0.1388888888888889</v>
+        <v>5</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>80</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>0.0125</v>
+        <v>1</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>46</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>0.4782608695652174</v>
+        <v>22</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>49</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>0.06122448979591837</v>
+        <v>3</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>86</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>0.01162790697674419</v>
+        <v>1</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>19</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>0.1052631578947368</v>
+        <v>2</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>27</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>0.03703703703703703</v>
+        <v>1</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>44</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2720</v>
+        <v>2867</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2209</v>
+        <v>2301</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>610</v>
+        <v>653</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>435</v>
+        <v>475</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>494</v>
+        <v>519</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="J12" s="12" t="n">
         <v>125</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>102</v>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>12</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>55</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,28 +1037,28 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>6</v>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>11</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,28 +1145,28 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>24</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="J17" s="12" t="n">
         <v>24</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>9</v>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>3</v>
@@ -1211,19 +1211,19 @@
         <v>21</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>23</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1253,25 +1253,25 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F19" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="I19" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="G19" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="H19" s="12" t="n">
-        <v>67</v>
-      </c>
-      <c r="I19" s="12" t="n">
-        <v>73</v>
-      </c>
       <c r="J19" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L19" s="12" t="n">
         <v>29</v>
@@ -1307,35 +1307,35 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>26</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1361,28 +1361,28 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>15</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
@@ -1415,28 +1415,28 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>22</v>
@@ -1469,19 +1469,19 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>8</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="J23" s="12" t="n">
         <v>22</v>
@@ -1490,7 +1490,7 @@
         <v>13</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>4</v>
@@ -1526,13 +1526,13 @@
         <v>67</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>4</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>61</v>
@@ -1544,7 +1544,7 @@
         <v>11</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
@@ -1558,7 +1558,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>07221</t>
+          <t>17111</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>17111</t>
+          <t>07221</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,31 +1631,31 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1666,150 +1666,150 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>57176</t>
+          <t>27224</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr"/>
+          <t>CAMPAGNANO DI ROMA</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>27224</t>
+          <t>54638</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CAMPAGNANO DI ROMA</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+          <t>VITERBO</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr"/>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>54638</t>
+          <t>57176</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>VITERBO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr"/>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="F29" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="G29" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="H29" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1820,104 +1820,104 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07224</t>
+          <t>07132</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MARINO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Manzo Fabio</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>07132</t>
+          <t>07224</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>MARINO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Manzo Fabio</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
         <v>47</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="G31" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="H31" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="I31" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="J31" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="K31" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H31" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="I31" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="J31" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="K31" s="12" t="n">
-        <v>7</v>
-      </c>
       <c r="L31" s="12" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1947,19 +1947,19 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F32" s="12" t="n">
         <v>35</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J32" s="12" t="n">
         <v>12</v>
@@ -1968,14 +1968,14 @@
         <v>11</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>3</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2001,13 +2001,13 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>6</v>
@@ -2019,10 +2019,10 @@
         <v>11</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>2</v>
@@ -2067,16 +2067,16 @@
         <v>19</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>36953</t>
+          <t>58342</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2105,105 +2105,105 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G35" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I35" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="J35" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="K35" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H35" s="12" t="n">
+      <c r="L35" s="12" t="n">
+        <v>86</v>
+      </c>
+      <c r="M35" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I35" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="J35" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="K35" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" s="12" t="n">
-        <v>134</v>
-      </c>
-      <c r="M35" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>36942</t>
+          <t>36953</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>CASTEL GANDOLFO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Manzo Fabio</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>36</v>
+        <v>143</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>07143</t>
+          <t>36942</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CASTEL GANDOLFO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2213,46 +2213,46 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F37" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I37" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="G37" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="H37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="12" t="n">
-        <v>22</v>
-      </c>
       <c r="J37" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K37" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L37" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="M37" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K37" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="L37" s="12" t="n">
-        <v>78</v>
-      </c>
-      <c r="M37" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>58342</t>
+          <t>07143</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2262,37 +2262,37 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Manzo Fabio</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>1</v>
@@ -2306,7 +2306,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>55307</t>
+          <t>27100</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H39" s="12" t="n">
         <v>0</v>
@@ -2343,17 +2343,17 @@
         <v>7</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2379,28 +2379,28 @@
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M40" s="12" t="n">
         <v>0</v>
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G41" s="12" t="n">
         <v>1</v>
@@ -2451,10 +2451,10 @@
         <v>3</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M41" s="12" t="n">
         <v>0</v>
@@ -2468,7 +2468,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>27100</t>
+          <t>55307</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2487,42 +2487,42 @@
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K42" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L42" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="M42" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L42" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="M42" s="12" t="n">
-        <v>22</v>
-      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>58264</t>
+          <t>36981</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Manzo Fabio</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2541,31 +2541,31 @@
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J43" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="12" t="n">
+        <v>91</v>
+      </c>
+      <c r="M43" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="L43" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="M43" s="12" t="n">
-        <v>3</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>36981</t>
+          <t>58264</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Manzo Fabio</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2595,31 +2595,31 @@
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="G44" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="H44" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="I44" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="J44" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K44" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H44" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="J44" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="K44" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L44" s="12" t="n">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>19</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H45" s="12" t="n">
         <v>12</v>
@@ -2670,10 +2670,10 @@
         <v>5</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
@@ -2706,13 +2706,13 @@
         <v>11</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>18</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I46" s="12" t="n">
         <v>19</v>
@@ -2724,7 +2724,7 @@
         <v>0</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="M46" s="12" t="n">
         <v>0</v>
@@ -2774,14 +2774,14 @@
         <v>0</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2810,7 @@
         <v>9</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>0</v>
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F50" s="12" t="n">
         <v>0</v>
@@ -2923,7 +2923,7 @@
         <v>0</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J50" s="12" t="n">
         <v>2</v>
@@ -2982,7 +2982,7 @@
         <v>3</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M51" s="12" t="n">
         <v>1</v>
@@ -3018,7 +3018,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G52" s="12" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
         <v>0</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G53" s="12" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
         <v>0</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G54" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
@@ -1728,7 +1728,11 @@
           <t>VITERBO</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
           <t>DELLA ROSA FABIO</t>
@@ -1778,7 +1782,11 @@
           <t>ROMA</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
           <t>CASINI GIUSEPPE NICCOLO'</t>
@@ -2746,7 +2754,11 @@
           <t>MORLUPO</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
           <t>DELLA ROSA FABIO</t>
@@ -2904,7 +2916,11 @@
           <t>ROMA</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
           <t>MARIANI MARIO</t>
@@ -2954,7 +2970,11 @@
           <t>ROMA</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
           <t>LESTI LEONARDO</t>
@@ -3058,7 +3078,11 @@
           <t>ROMA</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
           <t>GIOVANNINI DANIELE</t>

--- a/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>44</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2867</v>
+        <v>3064</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2301</v>
+        <v>2431</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>653</v>
+        <v>718</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>475</v>
+        <v>504</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="K11" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="L11" s="12" t="n">
+        <v>542</v>
+      </c>
+      <c r="M11" s="12" t="n">
         <v>78</v>
-      </c>
-      <c r="L11" s="12" t="n">
-        <v>519</v>
-      </c>
-      <c r="M11" s="12" t="n">
-        <v>73</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>40</v>
@@ -887,19 +887,19 @@
         <v>36</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>32</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>408</v>
+        <v>435</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>360</v>
+        <v>385</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,35 +983,35 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>12</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="J14" s="12" t="n">
         <v>45</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1037,28 +1037,28 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>6</v>
@@ -1091,28 +1091,28 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>11</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>2</v>
@@ -1145,31 +1145,31 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>24</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>3</v>
@@ -1217,10 +1217,10 @@
         <v>43</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>44</v>
@@ -1234,17 +1234,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07473</t>
+          <t>06905</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>MONTEFIASCONE</t>
+          <t>RIETI</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Scagnetti Giampiero</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1253,52 +1253,52 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06905</t>
+          <t>07473</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>RIETI</t>
+          <t>MONTEFIASCONE</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Scagnetti Giampiero</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1307,31 +1307,31 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>16968</t>
+          <t>17111</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>FIUMICINO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,39 +1357,39 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>92</v>
+        <v>139</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1415,31 +1415,31 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>8</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J22" s="12" t="n">
         <v>21</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1450,12 +1450,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>80008</t>
+          <t>16968</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>FIUMICINO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,35 +1465,35 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>205</v>
+        <v>100</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1504,50 +1504,50 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>07049</t>
+          <t>80008</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>FRASCATI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Manzo Fabio</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>159</v>
+        <v>96</v>
       </c>
       <c r="G24" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H24" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="I24" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="J24" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="K24" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L24" s="12" t="n">
+        <v>219</v>
+      </c>
+      <c r="M24" s="12" t="n">
         <v>4</v>
-      </c>
-      <c r="H24" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="I24" s="12" t="n">
-        <v>61</v>
-      </c>
-      <c r="J24" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="K24" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="L24" s="12" t="n">
-        <v>239</v>
-      </c>
-      <c r="M24" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1558,54 +1558,54 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>17111</t>
+          <t>07049</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>FRASCATI</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Manzo Fabio</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>69</v>
+        <v>161</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>132</v>
+        <v>254</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1631,28 +1631,28 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>25</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>5</v>
@@ -1666,12 +1666,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>27224</t>
+          <t>54638</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>CAMPAGNANO DI ROMA</t>
+          <t>VITERBO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,51 +1681,51 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>60</v>
+        <v>107</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>54638</t>
+          <t>57176</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>VITERBO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,51 +1735,51 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>57176</t>
+          <t>27224</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CAMPAGNANO DI ROMA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,147 +1789,147 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07132</t>
+          <t>07224</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>MARINO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Manzo Fabio</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
         <v>51</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="G30" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="H30" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="I30" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="J30" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="K30" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H30" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="I30" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="J30" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="K30" s="12" t="n">
-        <v>10</v>
-      </c>
       <c r="L30" s="12" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>07224</t>
+          <t>07132</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MARINO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Manzo Fabio</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
         <v>43</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>6</v>
@@ -1976,14 +1976,14 @@
         <v>11</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>3</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>9</v>
@@ -2021,7 +2021,7 @@
         <v>6</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J33" s="12" t="n">
         <v>11</v>
@@ -2030,7 +2030,7 @@
         <v>10</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>2</v>
@@ -2075,16 +2075,16 @@
         <v>19</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>0</v>
@@ -2098,7 +2098,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>58342</t>
+          <t>36953</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2113,35 +2113,35 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
         <v>34</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>86</v>
+        <v>156</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>36953</t>
+          <t>58342</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2167,39 +2167,39 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G36" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H36" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H36" s="12" t="n">
+      <c r="I36" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="J36" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="K36" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L36" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="M36" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I36" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="J36" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="K36" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" s="12" t="n">
-        <v>143</v>
-      </c>
-      <c r="M36" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
         <v>32</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>0</v>
@@ -2279,19 +2279,19 @@
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F38" s="12" t="n">
         <v>21</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J38" s="12" t="n">
         <v>5</v>
@@ -2300,134 +2300,134 @@
         <v>6</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>27100</t>
+          <t>58351</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>VALMONTONE</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Funari Emanuele</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J39" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K39" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="K39" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="L39" s="12" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>58351</t>
+          <t>55307</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>VALMONTONE</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Funari Emanuele</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
         <v>27</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>55811</t>
+          <t>27100</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>POMEZIA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2437,35 +2437,35 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G41" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="H41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="J41" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K41" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="J41" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K41" s="12" t="n">
-        <v>10</v>
-      </c>
       <c r="L41" s="12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -2476,12 +2476,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>55307</t>
+          <t>55811</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>POMEZIA</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2491,39 +2491,39 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2549,19 +2549,19 @@
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G43" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J43" s="12" t="n">
         <v>8</v>
@@ -2570,14 +2570,14 @@
         <v>0</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2606,13 +2606,13 @@
         <v>23</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>8</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I44" s="12" t="n">
         <v>22</v>
@@ -2624,7 +2624,7 @@
         <v>1</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="M44" s="12" t="n">
         <v>3</v>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F45" s="12" t="n">
         <v>19</v>
@@ -2669,7 +2669,7 @@
         <v>12</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J45" s="12" t="n">
         <v>1</v>
@@ -2678,7 +2678,7 @@
         <v>5</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M45" s="12" t="n">
         <v>2</v>
@@ -2711,7 +2711,7 @@
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F46" s="12" t="n">
         <v>31</v>
@@ -2720,10 +2720,10 @@
         <v>18</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J46" s="12" t="n">
         <v>4</v>
@@ -2732,7 +2732,7 @@
         <v>0</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="M46" s="12" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F47" s="12" t="n">
         <v>0</v>
@@ -2777,7 +2777,7 @@
         <v>0</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J47" s="12" t="n">
         <v>3</v>
@@ -2786,14 +2786,14 @@
         <v>0</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
         <v>9</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>0</v>
@@ -2942,7 +2942,7 @@
         <v>8</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K50" s="12" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
         <v>2</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G52" s="12" t="n">
         <v>0</v>
@@ -3092,13 +3092,13 @@
         <v>0</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I53" s="12" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
         <v>0</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G54" s="12" t="n">
         <v>0</v>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>44</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3064</v>
+        <v>3271</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2431</v>
+        <v>2569</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>718</v>
+        <v>794</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>363</v>
+        <v>394</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>504</v>
+        <v>536</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>542</v>
+        <v>584</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>323</v>
+        <v>339</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>399</v>
+        <v>428</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>435</v>
+        <v>461</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>385</v>
+        <v>409</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>12</v>
@@ -995,19 +995,19 @@
         <v>12</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,28 +1037,28 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>6</v>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>11</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>39</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,35 +1145,35 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>24</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>10</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>39</v>
@@ -1208,22 +1208,22 @@
         <v>3</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1234,17 +1234,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>06905</t>
+          <t>07473</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>RIETI</t>
+          <t>MONTEFIASCONE</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Scagnetti Giampiero</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1253,52 +1253,52 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>07473</t>
+          <t>06905</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>MONTEFIASCONE</t>
+          <t>RIETI</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Scagnetti Giampiero</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1307,31 +1307,31 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>30</v>
+        <v>93</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>6</v>
@@ -1373,16 +1373,16 @@
         <v>29</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>4</v>
@@ -1396,50 +1396,50 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>56322</t>
+          <t>16968</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>FIUMICINO</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Manzo Fabio</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>194</v>
+        <v>126</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>224</v>
+        <v>108</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1450,50 +1450,50 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>16968</t>
+          <t>56322</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>FIUMICINO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Manzo Fabio</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>119</v>
+        <v>213</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>100</v>
+        <v>233</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1523,28 +1523,28 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>4</v>
@@ -1577,28 +1577,28 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
@@ -1631,28 +1631,28 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H26" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="I26" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="J26" s="12" t="n">
         <v>25</v>
-      </c>
-      <c r="I26" s="12" t="n">
-        <v>57</v>
-      </c>
-      <c r="J26" s="12" t="n">
-        <v>23</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>5</v>
@@ -1666,12 +1666,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>54638</t>
+          <t>57176</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>VITERBO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,35 +1681,35 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>107</v>
+        <v>58</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1720,12 +1720,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>57176</t>
+          <t>54638</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>VITERBO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,39 +1735,39 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>55</v>
+        <v>111</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1793,28 +1793,28 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
@@ -1847,35 +1847,35 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F30" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="H30" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="I30" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="G30" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="H30" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="I30" s="12" t="n">
-        <v>47</v>
-      </c>
       <c r="J30" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1904,13 +1904,13 @@
         <v>51</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>37</v>
@@ -1922,7 +1922,7 @@
         <v>10</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
@@ -1955,35 +1955,35 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>3</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2009,28 +2009,28 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>6</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>10</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
@@ -2063,28 +2063,28 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>0</v>
@@ -2098,54 +2098,54 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>36953</t>
+          <t>36942</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CASTEL GANDOLFO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Manzo Fabio</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>156</v>
+        <v>38</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2171,19 +2171,19 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J36" s="12" t="n">
         <v>11</v>
@@ -2192,68 +2192,68 @@
         <v>6</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>36942</t>
+          <t>36953</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>CASTEL GANDOLFO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Manzo Fabio</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="F37" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="F37" s="12" t="n">
-        <v>51</v>
-      </c>
       <c r="G37" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>37</v>
+        <v>170</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F38" s="12" t="n">
         <v>21</v>
@@ -2291,16 +2291,16 @@
         <v>0</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>1</v>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G39" s="12" t="n">
         <v>0</v>
@@ -2345,23 +2345,23 @@
         <v>4</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K39" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F40" s="12" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J40" s="12" t="n">
         <v>7</v>
@@ -2408,26 +2408,26 @@
         <v>3</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="M40" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>27100</t>
+          <t>55811</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>POMEZIA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2437,35 +2437,35 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -2476,12 +2476,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>55811</t>
+          <t>36981</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>POMEZIA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2491,46 +2491,46 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
         <v>27</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G42" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J42" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K42" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K42" s="12" t="n">
-        <v>11</v>
-      </c>
       <c r="L42" s="12" t="n">
-        <v>51</v>
+        <v>101</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>36981</t>
+          <t>27100</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2549,35 +2549,35 @@
         </is>
       </c>
       <c r="E43" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="F43" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="G43" s="12" t="n">
+      <c r="H43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="J43" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K43" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H43" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="I43" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="J43" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="K43" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L43" s="12" t="n">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2603,19 +2603,19 @@
         </is>
       </c>
       <c r="E44" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="G44" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H44" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I44" s="12" t="n">
         <v>23</v>
-      </c>
-      <c r="F44" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="G44" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="H44" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="I44" s="12" t="n">
-        <v>22</v>
       </c>
       <c r="J44" s="12" t="n">
         <v>9</v>
@@ -2624,7 +2624,7 @@
         <v>1</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M44" s="12" t="n">
         <v>3</v>
@@ -2657,31 +2657,31 @@
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G45" s="12" t="n">
         <v>7</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
@@ -2692,12 +2692,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>07084</t>
+          <t>59309</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MORLUPO</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2707,23 +2707,23 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J46" s="12" t="n">
         <v>4</v>
@@ -2732,26 +2732,26 @@
         <v>0</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="M46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>59309</t>
+          <t>07084</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>MORLUPO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2761,39 +2761,39 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="M47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
         <v>9</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F51" s="12" t="n">
         <v>0</v>
@@ -2993,7 +2993,7 @@
         <v>0</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J51" s="12" t="n">
         <v>0</v>
@@ -3002,10 +3002,10 @@
         <v>3</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>0</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G53" s="12" t="n">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I54" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>44</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3271</v>
+        <v>3451</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2569</v>
+        <v>2715</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>794</v>
+        <v>865</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>536</v>
+        <v>553</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>584</v>
+        <v>617</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>428</v>
+        <v>455</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>378</v>
+        <v>403</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>105</v>
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>237</v>
+        <v>265</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>461</v>
+        <v>488</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>409</v>
+        <v>434</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,28 +1037,28 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>6</v>
@@ -1091,28 +1091,28 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>3</v>
@@ -1145,28 +1145,28 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>22</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>10</v>
@@ -1199,28 +1199,28 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>22</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>45</v>
@@ -1234,17 +1234,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07473</t>
+          <t>06905</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>MONTEFIASCONE</t>
+          <t>RIETI</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Scagnetti Giampiero</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1253,52 +1253,52 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06905</t>
+          <t>07473</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>RIETI</t>
+          <t>MONTEFIASCONE</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Scagnetti Giampiero</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1307,31 +1307,31 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>93</v>
+        <v>36</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>17111</t>
+          <t>16968</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>FIUMICINO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,51 +1357,51 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>16968</t>
+          <t>17111</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>FIUMICINO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,39 +1411,39 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1469,31 +1469,31 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>18</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1523,19 +1523,19 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J24" s="12" t="n">
         <v>24</v>
@@ -1544,10 +1544,10 @@
         <v>13</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1577,19 +1577,19 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J25" s="12" t="n">
         <v>25</v>
@@ -1598,7 +1598,7 @@
         <v>17</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>266</v>
+        <v>289</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
@@ -1612,7 +1612,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07221</t>
+          <t>57176</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1627,46 +1627,46 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="K26" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L26" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="M26" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L26" s="12" t="n">
-        <v>147</v>
-      </c>
-      <c r="M26" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>57176</t>
+          <t>07221</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1681,39 +1681,39 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>58</v>
+        <v>153</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1742,13 +1742,13 @@
         <v>65</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>4</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>42</v>
@@ -1760,10 +1760,10 @@
         <v>24</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1793,28 +1793,28 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
@@ -1847,35 +1847,35 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="H30" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="I30" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="F30" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="G30" s="12" t="n">
-        <v>55</v>
-      </c>
-      <c r="H30" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="I30" s="12" t="n">
-        <v>50</v>
-      </c>
       <c r="J30" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>2</v>
@@ -1913,13 +1913,13 @@
         <v>9</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J31" s="12" t="n">
         <v>11</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>66</v>
@@ -1936,12 +1936,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>07181</t>
+          <t>59331</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SUBIACO</t>
+          <t>MONTALTO DI CASTRO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,51 +1951,51 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="G32" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="H32" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H32" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="I32" s="12" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>59331</t>
+          <t>07181</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>MONTALTO DI CASTRO</t>
+          <t>SUBIACO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,35 +2005,35 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2063,19 +2063,19 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J34" s="12" t="n">
         <v>12</v>
@@ -2084,10 +2084,10 @@
         <v>6</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2117,31 +2117,31 @@
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J35" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>58342</t>
+          <t>36953</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2167,35 +2167,35 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>96</v>
+        <v>183</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>36953</t>
+          <t>58342</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2221,35 +2221,35 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H37" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I37" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="F37" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="G37" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="H37" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I37" s="12" t="n">
-        <v>43</v>
-      </c>
       <c r="J37" s="12" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K37" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L37" s="12" t="n">
+        <v>104</v>
+      </c>
+      <c r="M37" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="L37" s="12" t="n">
-        <v>170</v>
-      </c>
-      <c r="M37" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2279,28 +2279,28 @@
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F38" s="12" t="n">
         <v>21</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>1</v>
@@ -2333,28 +2333,28 @@
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J39" s="12" t="n">
         <v>11</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>0</v>
@@ -2368,12 +2368,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>55307</t>
+          <t>55811</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>POMEZIA</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2383,35 +2383,35 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2422,12 +2422,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>55811</t>
+          <t>36981</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>POMEZIA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2437,46 +2437,46 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
         <v>28</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G41" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I41" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="J41" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K41" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L41" s="12" t="n">
+        <v>114</v>
+      </c>
+      <c r="M41" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I41" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="J41" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K41" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="L41" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="M41" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>36981</t>
+          <t>55307</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2495,35 +2495,35 @@
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I42" s="12" t="n">
         <v>29</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K42" s="12" t="n">
         <v>3</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="M42" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2606,13 +2606,13 @@
         <v>24</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>9</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I44" s="12" t="n">
         <v>23</v>
@@ -2624,14 +2624,14 @@
         <v>1</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="M44" s="12" t="n">
         <v>3</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
         <v>19</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G45" s="12" t="n">
         <v>7</v>
@@ -2678,7 +2678,7 @@
         <v>7</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="M45" s="12" t="n">
         <v>3</v>
@@ -2692,12 +2692,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>59309</t>
+          <t>07084</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>MORLUPO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2707,51 +2707,51 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="M46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>07084</t>
+          <t>59309</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MORLUPO</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2761,23 +2761,23 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J47" s="12" t="n">
         <v>4</v>
@@ -2786,14 +2786,14 @@
         <v>0</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>87</v>
+        <v>16</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
         <v>9</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>0</v>
@@ -2948,7 +2948,7 @@
         <v>0</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M50" s="12" t="n">
         <v>0</v>
@@ -3002,14 +3002,14 @@
         <v>3</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M51" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3092,13 +3092,13 @@
         <v>0</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I53" s="12" t="n">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I54" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
@@ -2808,11 +2808,7 @@
           <t>LADISPOLI</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Scagnetti Giampiero</t>
-        </is>
-      </c>
+      <c r="C48" s="2" t="inlineStr"/>
       <c r="D48" s="2" t="inlineStr">
         <is>
           <t>GIOVANNINI DANIELE</t>
@@ -3078,11 +3074,7 @@
           <t>ROMA</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+      <c r="C53" s="2" t="inlineStr"/>
       <c r="D53" s="2" t="inlineStr">
         <is>
           <t>GIOVANNINI DANIELE</t>
@@ -3132,11 +3124,7 @@
           <t>ROMA</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Scagnetti Giampiero</t>
-        </is>
-      </c>
+      <c r="C54" s="2" t="inlineStr"/>
       <c r="D54" s="2" t="inlineStr">
         <is>
           <t>CASINI GIUSEPPE NICCOLO'</t>

--- a/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
@@ -209,23 +209,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N54" headerRowCount="1">
-  <autoFilter ref="A10:N54"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O54" headerRowCount="1">
+  <autoFilter ref="A10:O54"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
-    <tableColumn id="3" name="Agente"/>
-    <tableColumn id="4" name="CR"/>
-    <tableColumn id="5" name="Vend 2026"/>
-    <tableColumn id="6" name="Vend 2025"/>
-    <tableColumn id="7" name="Ass 2026"/>
-    <tableColumn id="8" name="Ass 2025"/>
-    <tableColumn id="9" name="Prospect"/>
-    <tableColumn id="10" name="Twin"/>
-    <tableColumn id="11" name="Business"/>
-    <tableColumn id="12" name="Sost anno"/>
-    <tableColumn id="13" name="UP EU"/>
-    <tableColumn id="14" name="Stato"/>
+    <tableColumn id="3" name="Indirizzo"/>
+    <tableColumn id="4" name="Agente"/>
+    <tableColumn id="5" name="CR"/>
+    <tableColumn id="6" name="Vend 2026"/>
+    <tableColumn id="7" name="Vend 2025"/>
+    <tableColumn id="8" name="Ass 2026"/>
+    <tableColumn id="9" name="Ass 2025"/>
+    <tableColumn id="10" name="Prospect"/>
+    <tableColumn id="11" name="Twin"/>
+    <tableColumn id="12" name="Business"/>
+    <tableColumn id="13" name="Sost anno"/>
+    <tableColumn id="14" name="UP EU"/>
+    <tableColumn id="15" name="Stato"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -520,23 +521,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N54"/>
+  <dimension ref="A1:O54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -558,6 +560,7 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -574,6 +577,7 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -598,6 +602,7 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -622,6 +627,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -638,6 +644,7 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -670,6 +677,7 @@
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -694,6 +702,7 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -710,6 +719,7 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -726,6 +736,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -740,60 +751,65 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
+          <t>Indirizzo</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Vend 2026</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Vend 2025</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Ass 2026</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Ass 2025</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Twin</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Sost anno</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>UP EU</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
@@ -812,42 +828,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>TIBURTINA 0400</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>413</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>553</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>197</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="I11" s="12" t="n">
         <v>123</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="J11" s="12" t="n">
         <v>318</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="K11" s="12" t="n">
         <v>121</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="L11" s="12" t="n">
         <v>97</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="M11" s="12" t="n">
         <v>617</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="N11" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -866,42 +887,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>VIA TIBURTINA KM 19,800 0145</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>354</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>455</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="H12" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="I12" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="J12" s="12" t="n">
         <v>278</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="K12" s="12" t="n">
         <v>147</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="L12" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="M12" s="12" t="n">
         <v>403</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="N12" s="12" t="n">
         <v>105</v>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -920,42 +946,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>VIA LAURENTINA 453</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>265</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>289</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="I13" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="J13" s="12" t="n">
         <v>205</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="K13" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="L13" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="M13" s="12" t="n">
         <v>488</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="N13" s="12" t="n">
         <v>434</v>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -974,42 +1005,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>S.S. AURELIA KM 68+885</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>201</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>200</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="I14" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="J14" s="12" t="n">
         <v>144</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="K14" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="L14" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="M14" s="12" t="n">
         <v>266</v>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="N14" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1028,42 +1064,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>CASILINA,  0928</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>Funari Emanuele</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>MARIANI MARIO</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>193</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>255</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="H15" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="I15" s="12" t="n">
         <v>218</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="J15" s="12" t="n">
         <v>137</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="K15" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="L15" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="L15" s="12" t="n">
+      <c r="M15" s="12" t="n">
         <v>193</v>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="N15" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1082,42 +1123,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>VIA CASILINA KM. 24+950</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>MARIANI MARIO</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>163</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>235</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="I16" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="J16" s="12" t="n">
         <v>103</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="K16" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="L16" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="M16" s="12" t="n">
         <v>257</v>
       </c>
-      <c r="M16" s="12" t="n">
+      <c r="N16" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1136,42 +1182,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>CORSO DI FRANCIA 80</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>153</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>182</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="H17" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="I17" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="I17" s="12" t="n">
+      <c r="J17" s="12" t="n">
         <v>136</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="K17" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="L17" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="L17" s="12" t="n">
+      <c r="M17" s="12" t="n">
         <v>224</v>
       </c>
-      <c r="M17" s="12" t="n">
+      <c r="N17" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1190,42 +1241,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>S.S.4 DIR. KM. 3 + 400</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>DELLA ROSA FABIO</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>121</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="H18" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H18" s="12" t="n">
+      <c r="I18" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="J18" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="K18" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="K18" s="12" t="n">
+      <c r="L18" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="L18" s="12" t="n">
+      <c r="M18" s="12" t="n">
         <v>140</v>
       </c>
-      <c r="M18" s="12" t="n">
+      <c r="N18" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1244,42 +1300,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>S.S.4 KM.87+602</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>Scagnetti Giampiero</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>DELLA ROSA FABIO</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>104</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>112</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="H19" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="H19" s="12" t="n">
+      <c r="I19" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I19" s="12" t="n">
+      <c r="J19" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="J19" s="12" t="n">
+      <c r="K19" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="K19" s="12" t="n">
+      <c r="L19" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="M19" s="12" t="n">
         <v>101</v>
       </c>
-      <c r="M19" s="12" t="n">
+      <c r="N19" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1298,42 +1359,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>SS 2 CASSIA KM 97+800</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>DELLA ROSA FABIO</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>103</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>94</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="H20" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="H20" s="12" t="n">
+      <c r="I20" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="I20" s="12" t="n">
+      <c r="J20" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="K20" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="K20" s="12" t="n">
+      <c r="L20" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="M20" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="M20" s="12" t="n">
+      <c r="N20" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1352,42 +1418,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>VIA PORTUENSE 2468</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>133</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="H21" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="H21" s="12" t="n">
+      <c r="I21" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="I21" s="12" t="n">
+      <c r="J21" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="J21" s="12" t="n">
+      <c r="K21" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="K21" s="12" t="n">
+      <c r="L21" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="M21" s="12" t="n">
         <v>119</v>
       </c>
-      <c r="M21" s="12" t="n">
+      <c r="N21" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1406,42 +1477,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>SS SALARIA KM 14, 895 EST</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>96</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="H22" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H22" s="12" t="n">
+      <c r="I22" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="I22" s="12" t="n">
+      <c r="J22" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="J22" s="12" t="n">
+      <c r="K22" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="K22" s="12" t="n">
+      <c r="L22" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="L22" s="12" t="n">
+      <c r="M22" s="12" t="n">
         <v>155</v>
       </c>
-      <c r="M22" s="12" t="n">
+      <c r="N22" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1460,42 +1536,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>VIA AURELIA 711</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
           <t>Manzo Fabio</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>LESTI LEONARDO</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>227</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="H23" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="H23" s="12" t="n">
+      <c r="I23" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="I23" s="12" t="n">
+      <c r="J23" s="12" t="n">
         <v>78</v>
       </c>
-      <c r="J23" s="12" t="n">
+      <c r="K23" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="K23" s="12" t="n">
+      <c r="L23" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="L23" s="12" t="n">
+      <c r="M23" s="12" t="n">
         <v>250</v>
       </c>
-      <c r="M23" s="12" t="n">
+      <c r="N23" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1514,42 +1595,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>CORSO FRANCIA</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>101</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="H24" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="H24" s="12" t="n">
+      <c r="I24" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="I24" s="12" t="n">
+      <c r="J24" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="J24" s="12" t="n">
+      <c r="K24" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="K24" s="12" t="n">
+      <c r="L24" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="L24" s="12" t="n">
+      <c r="M24" s="12" t="n">
         <v>250</v>
       </c>
-      <c r="M24" s="12" t="n">
+      <c r="N24" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1568,42 +1654,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>VIA VITTORIO VENETO 34</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>Manzo Fabio</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>MARIANI MARIO</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>181</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="H25" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H25" s="12" t="n">
+      <c r="I25" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="I25" s="12" t="n">
+      <c r="J25" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="J25" s="12" t="n">
+      <c r="K25" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="K25" s="12" t="n">
+      <c r="L25" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="L25" s="12" t="n">
+      <c r="M25" s="12" t="n">
         <v>289</v>
       </c>
-      <c r="M25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="N25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1622,42 +1713,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>VIA CASILINA KM 12+943, 1423</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="F26" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="H26" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="12" t="n">
         <v>61</v>
       </c>
-      <c r="J26" s="12" t="n">
+      <c r="K26" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="K26" s="12" t="n">
+      <c r="L26" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L26" s="12" t="n">
+      <c r="M26" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="M26" s="12" t="n">
+      <c r="N26" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1676,42 +1772,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>VIA TAGLIAMENTO 0049</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="H27" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="H27" s="12" t="n">
+      <c r="I27" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="I27" s="12" t="n">
+      <c r="J27" s="12" t="n">
         <v>61</v>
       </c>
-      <c r="J27" s="12" t="n">
+      <c r="K27" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="K27" s="12" t="n">
+      <c r="L27" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L27" s="12" t="n">
+      <c r="M27" s="12" t="n">
         <v>153</v>
       </c>
-      <c r="M27" s="12" t="n">
+      <c r="N27" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1730,42 +1831,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>TANGENZIALE OVEST N 15</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>DELLA ROSA FABIO</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="H28" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H28" s="12" t="n">
+      <c r="I28" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I28" s="12" t="n">
+      <c r="J28" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="J28" s="12" t="n">
+      <c r="K28" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="K28" s="12" t="n">
+      <c r="L28" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="L28" s="12" t="n">
+      <c r="M28" s="12" t="n">
         <v>121</v>
       </c>
-      <c r="M28" s="12" t="n">
+      <c r="N28" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1784,42 +1890,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>SS 2 CASSIA BIS KM30</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>MARIANI MARIO</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="H29" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H29" s="12" t="n">
+      <c r="I29" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="I29" s="12" t="n">
+      <c r="J29" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="J29" s="12" t="n">
+      <c r="K29" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="K29" s="12" t="n">
+      <c r="L29" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="L29" s="12" t="n">
+      <c r="M29" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="M29" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="N29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1838,42 +1949,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>CIRCONVALLAZIONE GIANICOLENSE 340</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>LESTI LEONARDO</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>61</v>
       </c>
-      <c r="G30" s="12" t="n">
+      <c r="H30" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="H30" s="12" t="n">
+      <c r="I30" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="I30" s="12" t="n">
+      <c r="J30" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="J30" s="12" t="n">
+      <c r="K30" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="K30" s="12" t="n">
+      <c r="L30" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L30" s="12" t="n">
+      <c r="M30" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="M30" s="12" t="n">
+      <c r="N30" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1892,42 +2008,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>APPIA NUOVA KM 18+934 0006</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
           <t>Manzo Fabio</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>MARIANI MARIO</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="G31" s="12" t="n">
+      <c r="H31" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H31" s="12" t="n">
+      <c r="I31" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I31" s="12" t="n">
+      <c r="J31" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="J31" s="12" t="n">
+      <c r="K31" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="K31" s="12" t="n">
+      <c r="L31" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L31" s="12" t="n">
+      <c r="M31" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="M31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="N31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1946,42 +2067,47 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>S.S. 1 AURELIA SUD KM 107+200</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>DELLA ROSA FABIO</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="G32" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="G32" s="12" t="n">
+      <c r="H32" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="H32" s="12" t="n">
+      <c r="I32" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I32" s="12" t="n">
+      <c r="J32" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="J32" s="12" t="n">
+      <c r="K32" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K32" s="12" t="n">
+      <c r="L32" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L32" s="12" t="n">
+      <c r="M32" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="M32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="N32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2000,42 +2126,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>SUBLACENSE KM 72*883</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="F33" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="G33" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="G33" s="12" t="n">
+      <c r="H33" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H33" s="12" t="n">
+      <c r="I33" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I33" s="12" t="n">
+      <c r="J33" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="J33" s="12" t="n">
+      <c r="K33" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="K33" s="12" t="n">
+      <c r="L33" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L33" s="12" t="n">
+      <c r="M33" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="M33" s="12" t="n">
+      <c r="N33" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2054,42 +2185,47 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>VIA NOMENTANA, 850</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="F34" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="G34" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="H34" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H34" s="12" t="n">
+      <c r="I34" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="I34" s="12" t="n">
+      <c r="J34" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="J34" s="12" t="n">
+      <c r="K34" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="K34" s="12" t="n">
+      <c r="L34" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L34" s="12" t="n">
+      <c r="M34" s="12" t="n">
         <v>177</v>
       </c>
-      <c r="M34" s="12" t="n">
+      <c r="N34" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2108,42 +2244,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>VIA MAREMMANA KM 26, 150</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
           <t>Manzo Fabio</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>MARIANI MARIO</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="G35" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I35" s="12" t="n">
+      <c r="J35" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="J35" s="12" t="n">
+      <c r="K35" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="K35" s="12" t="n">
+      <c r="L35" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="L35" s="12" t="n">
+      <c r="M35" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="M35" s="12" t="n">
+      <c r="N35" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2162,42 +2303,47 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>VIA ELSA DE GIORGI</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="F36" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="G36" s="12" t="n">
+      <c r="H36" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="H36" s="12" t="n">
+      <c r="I36" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I36" s="12" t="n">
+      <c r="J36" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="J36" s="12" t="n">
+      <c r="K36" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="K36" s="12" t="n">
+      <c r="L36" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L36" s="12" t="n">
+      <c r="M36" s="12" t="n">
         <v>183</v>
       </c>
-      <c r="M36" s="12" t="n">
+      <c r="N36" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2216,42 +2362,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>VIA GROTTA PERFETTA 546</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="F37" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="G37" s="12" t="n">
+      <c r="H37" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H37" s="12" t="n">
+      <c r="I37" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I37" s="12" t="n">
+      <c r="J37" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="J37" s="12" t="n">
+      <c r="K37" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="K37" s="12" t="n">
+      <c r="L37" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L37" s="12" t="n">
+      <c r="M37" s="12" t="n">
         <v>104</v>
       </c>
-      <c r="M37" s="12" t="n">
+      <c r="N37" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2270,42 +2421,47 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>VIA AURELIA KM 8,456</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
           <t>Manzo Fabio</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>LESTI LEONARDO</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="F38" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="G38" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="H38" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H38" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="J38" s="12" t="n">
+      <c r="K38" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="K38" s="12" t="n">
+      <c r="L38" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L38" s="12" t="n">
+      <c r="M38" s="12" t="n">
         <v>113</v>
       </c>
-      <c r="M38" s="12" t="n">
+      <c r="N38" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2324,42 +2480,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>VIA CASILINA KM 41</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
           <t>Funari Emanuele</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>MARIANI MARIO</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="F39" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="G39" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="G39" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I39" s="12" t="n">
+      <c r="J39" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="J39" s="12" t="n">
+      <c r="K39" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="K39" s="12" t="n">
+      <c r="L39" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L39" s="12" t="n">
+      <c r="M39" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="M39" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
+      <c r="N39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2378,42 +2539,47 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>VIA PONTINA KM 31+384</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="F40" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="G40" s="12" t="n">
         <v>45</v>
-      </c>
-      <c r="G40" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I40" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="J40" s="12" t="n">
+      <c r="K40" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K40" s="12" t="n">
+      <c r="L40" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L40" s="12" t="n">
+      <c r="M40" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="M40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="N40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2432,42 +2598,47 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>VIA COLLATINA 427, ANG. VIA PETITTI</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="F41" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="G41" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="G41" s="12" t="n">
+      <c r="H41" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="12" t="n">
+      <c r="I41" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I41" s="12" t="n">
+      <c r="J41" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="J41" s="12" t="n">
+      <c r="K41" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="K41" s="12" t="n">
+      <c r="L41" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L41" s="12" t="n">
+      <c r="M41" s="12" t="n">
         <v>114</v>
       </c>
-      <c r="M41" s="12" t="n">
+      <c r="N41" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2486,20 +2657,22 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>VIA CASILINA, 930</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="F42" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="F42" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G42" s="12" t="n">
         <v>0</v>
       </c>
@@ -2507,21 +2680,24 @@
         <v>0</v>
       </c>
       <c r="I42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="J42" s="12" t="n">
+      <c r="K42" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="K42" s="12" t="n">
+      <c r="L42" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L42" s="12" t="n">
+      <c r="M42" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="M42" s="12" t="n">
+      <c r="N42" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N42" s="2" t="inlineStr">
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2540,42 +2716,47 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>VIA CASILINA  110 110</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="F43" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="F43" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="H43" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="J43" s="12" t="n">
+      <c r="K43" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="K43" s="12" t="n">
+      <c r="L43" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L43" s="12" t="n">
+      <c r="M43" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="M43" s="12" t="n">
+      <c r="N43" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="N43" s="2" t="inlineStr">
+      <c r="O43" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2594,42 +2775,47 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>VIA CIAMPINO KM. 0+370 CAPANNELLE</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
           <t>Manzo Fabio</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="F44" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="G44" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="G44" s="12" t="n">
+      <c r="H44" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H44" s="12" t="n">
+      <c r="I44" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="I44" s="12" t="n">
+      <c r="J44" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="J44" s="12" t="n">
+      <c r="K44" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K44" s="12" t="n">
+      <c r="L44" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L44" s="12" t="n">
+      <c r="M44" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="M44" s="12" t="n">
+      <c r="N44" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N44" s="2" t="inlineStr">
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2648,42 +2834,47 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>VIA DI PONTE GALERIA  SNC - VIA DI PONTE GALERIA SNC</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>LESTI LEONARDO</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="F45" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="G45" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="G45" s="12" t="n">
+      <c r="H45" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H45" s="12" t="n">
+      <c r="I45" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="I45" s="12" t="n">
+      <c r="J45" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="J45" s="12" t="n">
+      <c r="K45" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K45" s="12" t="n">
+      <c r="L45" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="L45" s="12" t="n">
+      <c r="M45" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="M45" s="12" t="n">
+      <c r="N45" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N45" s="2" t="inlineStr">
+      <c r="O45" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2702,42 +2893,47 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>VIA TUSCOLANA ANG CAVE, 0432</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="F46" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="F46" s="12" t="n">
+      <c r="G46" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="G46" s="12" t="n">
+      <c r="H46" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="H46" s="12" t="n">
+      <c r="I46" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="I46" s="12" t="n">
+      <c r="J46" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="J46" s="12" t="n">
+      <c r="K46" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K46" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="M46" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
+      <c r="N46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2756,42 +2952,47 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>VIA FLAMINIA KM. 29,700 SNC</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>DELLA ROSA FABIO</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="F47" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="F47" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H47" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="J47" s="12" t="n">
+      <c r="K47" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K47" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="M47" s="12" t="n">
+      <c r="N47" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N47" s="2" t="inlineStr">
+      <c r="O47" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2808,40 +3009,45 @@
           <t>LADISPOLI</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr"/>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>VIA PALO LAZIALE 8</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="F48" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="G48" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="G48" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I48" s="12" t="n">
+      <c r="J48" s="12" t="n">
         <v>7</v>
-      </c>
-      <c r="J48" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="K48" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L48" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M48" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="M48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
+      <c r="N48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2860,20 +3066,22 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>VIA APPIA KM 24,600 SNC 0012</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>MARIANI MARIO</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="F49" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="F49" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G49" s="12" t="n">
         <v>0</v>
       </c>
@@ -2881,21 +3089,24 @@
         <v>0</v>
       </c>
       <c r="I49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="J49" s="12" t="n">
+      <c r="K49" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K49" s="12" t="n">
+      <c r="L49" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L49" s="12" t="n">
+      <c r="M49" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="M49" s="12" t="n">
+      <c r="N49" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N49" s="2" t="inlineStr">
+      <c r="O49" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2914,20 +3125,22 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
+          <t>VIA ARDEATINA</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>MARIANI MARIO</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="F50" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="F50" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G50" s="12" t="n">
         <v>0</v>
       </c>
@@ -2935,21 +3148,24 @@
         <v>0</v>
       </c>
       <c r="I50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="J50" s="12" t="n">
+      <c r="K50" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K50" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="M50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
+      <c r="N50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2968,42 +3184,47 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>VIA DELLA MAGLIANA 242</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>LESTI LEONARDO</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="F51" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="F51" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H51" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="J51" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="K51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L51" s="12" t="n">
+      <c r="M51" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="M51" s="12" t="n">
+      <c r="N51" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N51" s="2" t="inlineStr">
+      <c r="O51" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3022,42 +3243,47 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>VIA OSTIENSE 333</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>LESTI LEONARDO</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="F52" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F52" s="12" t="n">
+      <c r="G52" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="G52" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I52" s="12" t="n">
+      <c r="J52" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="J52" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="K52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="M52" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
+      <c r="N52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3074,27 +3300,29 @@
           <t>ROMA</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr"/>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>V. DON P. BORGHI ANG.JACH</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr"/>
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="G53" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I53" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J53" s="12" t="n">
         <v>0</v>
       </c>
@@ -3107,7 +3335,10 @@
       <c r="M53" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N53" s="2" t="inlineStr">
+      <c r="N53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3124,27 +3355,29 @@
           <t>ROMA</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr"/>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>S.P. 493 BRACCIANESE KM.11,500</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="G54" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I54" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J54" s="12" t="n">
         <v>0</v>
       </c>
@@ -3157,7 +3390,10 @@
       <c r="M54" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N54" s="2" t="inlineStr">
+      <c r="N54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>

--- a/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>44</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3451</v>
+        <v>3586</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2715</v>
+        <v>2837</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>865</v>
+        <v>922</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>553</v>
+        <v>577</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>97</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>617</v>
+        <v>649</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>455</v>
+        <v>471</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>403</v>
+        <v>420</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>289</v>
+        <v>313</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>488</v>
+        <v>520</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>434</v>
+        <v>464</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -995,118 +995,118 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>07171</t>
+          <t>07081</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CIVITAVECCHIA</t>
+          <t>COLLEFERRO</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>S.S. AURELIA KM 68+885</t>
+          <t>CASILINA,  0928</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Funari Emanuele</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>200</v>
+        <v>264</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>13</v>
+        <v>233</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>266</v>
+        <v>208</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>07081</t>
+          <t>07171</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>COLLEFERRO</t>
+          <t>CIVITAVECCHIA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>CASILINA,  0928</t>
+          <t>S.S. AURELIA KM 68+885</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Funari Emanuele</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>255</v>
+        <v>213</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>117</v>
+        <v>16</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>218</v>
+        <v>14</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>193</v>
+        <v>280</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>34</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>3</v>
@@ -1196,19 +1196,19 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>34</v>
@@ -1217,14 +1217,14 @@
         <v>22</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1255,28 +1255,28 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>30</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>45</v>
@@ -1290,22 +1290,22 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>06905</t>
+          <t>07473</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>RIETI</t>
+          <t>MONTEFIASCONE</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>S.S.4 KM.87+602</t>
+          <t>SS 2 CASSIA KM 97+800</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Scagnetti Giampiero</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1314,57 +1314,57 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>07473</t>
+          <t>06905</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>MONTEFIASCONE</t>
+          <t>RIETI</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>SS 2 CASSIA KM 97+800</t>
+          <t>S.S.4 KM.87+602</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Scagnetti Giampiero</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1373,31 +1373,31 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>91</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1432,28 +1432,28 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>2</v>
@@ -1491,19 +1491,19 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>6</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>19</v>
@@ -1512,7 +1512,7 @@
         <v>46</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>4</v>
@@ -1550,31 +1550,31 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>18</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1585,55 +1585,55 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>80008</t>
+          <t>07049</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>FRASCATI</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>CORSO FRANCIA</t>
+          <t>VIA VITTORIO VENETO 34</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Manzo Fabio</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>101</v>
+        <v>190</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>250</v>
+        <v>298</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1644,55 +1644,55 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>07049</t>
+          <t>80008</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>FRASCATI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIA VITTORIO VENETO 34</t>
+          <t>CORSO FRANCIA</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Manzo Fabio</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>181</v>
+        <v>105</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>289</v>
+        <v>261</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1727,28 +1727,28 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L26" s="12" t="n">
         <v>11</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>12</v>
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>5</v>
@@ -1845,19 +1845,19 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>12</v>
@@ -1866,7 +1866,7 @@
         <v>24</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>6</v>
@@ -1907,13 +1907,13 @@
         <v>65</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>38</v>
@@ -1925,7 +1925,7 @@
         <v>17</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>0</v>
@@ -1963,35 +1963,35 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="H30" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="I30" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="J30" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="I30" s="12" t="n">
-        <v>59</v>
-      </c>
-      <c r="J30" s="12" t="n">
-        <v>54</v>
-      </c>
       <c r="K30" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2022,28 +2022,28 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>0</v>
@@ -2084,13 +2084,13 @@
         <v>50</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>12</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J32" s="12" t="n">
         <v>39</v>
@@ -2102,7 +2102,7 @@
         <v>11</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>0</v>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>8</v>
@@ -2152,7 +2152,7 @@
         <v>4</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>14</v>
@@ -2161,69 +2161,69 @@
         <v>11</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>58258</t>
+          <t>36942</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CASTEL GANDOLFO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA NOMENTANA, 850</t>
+          <t>VIA MAREMMANA KM 26, 150</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Manzo Fabio</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I34" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J34" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="J34" s="12" t="n">
-        <v>38</v>
-      </c>
       <c r="K34" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L34" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="M34" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="N34" s="12" t="n">
         <v>6</v>
-      </c>
-      <c r="M34" s="12" t="n">
-        <v>177</v>
-      </c>
-      <c r="N34" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2234,55 +2234,55 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>36942</t>
+          <t>58258</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>CASTEL GANDOLFO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIA MAREMMANA KM 26, 150</t>
+          <t>VIA NOMENTANA, 850</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Manzo Fabio</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>44</v>
+        <v>180</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2317,10 +2317,10 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>13</v>
@@ -2335,17 +2335,17 @@
         <v>18</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2379,13 +2379,13 @@
         <v>37</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J37" s="12" t="n">
         <v>34</v>
@@ -2397,7 +2397,7 @@
         <v>6</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>1</v>
@@ -2444,7 +2444,7 @@
         <v>6</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" s="12" t="n">
         <v>28</v>
@@ -2456,14 +2456,14 @@
         <v>9</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H39" s="12" t="n">
         <v>0</v>
@@ -2506,7 +2506,7 @@
         <v>5</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K39" s="12" t="n">
         <v>11</v>
@@ -2515,7 +2515,7 @@
         <v>9</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>0</v>
@@ -2529,17 +2529,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>55811</t>
+          <t>36981</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>POMEZIA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>VIA PONTINA KM 31+384</t>
+          <t>VIA COLLATINA 427, ANG. VIA PETITTI</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2549,56 +2549,56 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I40" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J40" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="K40" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L40" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M40" s="12" t="n">
+        <v>120</v>
+      </c>
+      <c r="N40" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J40" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="K40" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="L40" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="M40" s="12" t="n">
-        <v>59</v>
-      </c>
-      <c r="N40" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>36981</t>
+          <t>55811</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>POMEZIA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>VIA COLLATINA 427, ANG. VIA PETITTI</t>
+          <t>VIA PONTINA KM 31+384</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2608,39 +2608,39 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G42" s="12" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K42" s="12" t="n">
         <v>7</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
         <v>1</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N43" s="12" t="n">
         <v>22</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>55</v>
@@ -2801,16 +2801,16 @@
         <v>15</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N44" s="12" t="n">
         <v>3</v>
@@ -2848,35 +2848,35 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I45" s="12" t="n">
         <v>13</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L45" s="12" t="n">
         <v>7</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N45" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2907,28 +2907,28 @@
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H46" s="12" t="n">
         <v>18</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>0</v>
@@ -2994,138 +2994,138 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>57171</t>
+          <t>55843</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>LADISPOLI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>VIA PALO LAZIALE 8</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr"/>
+          <t>VIA DELLA MAGLIANA 242</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
         <v>9</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K48" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M48" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="N48" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L48" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M48" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="N48" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>07164</t>
+          <t>57171</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>CASTEL GANDOLFO</t>
+          <t>LADISPOLI</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>VIA APPIA KM 24,600 SNC 0012</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+          <t>VIA PALO LAZIALE 8</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
         <v>9</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K49" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>58341</t>
+          <t>07164</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CASTEL GANDOLFO</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>VIA ARDEATINA</t>
+          <t>VIA APPIA KM 24,600 SNC 0012</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3139,7 +3139,7 @@
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G50" s="12" t="n">
         <v>0</v>
@@ -3151,19 +3151,19 @@
         <v>0</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>55843</t>
+          <t>58341</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>VIA DELLA MAGLIANA 242</t>
+          <t>VIA ARDEATINA</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3194,39 +3194,39 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="M51" s="12" t="n">
-        <v>34</v>
-      </c>
       <c r="N51" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3260,7 +3260,7 @@
         <v>2</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H52" s="12" t="n">
         <v>0</v>
@@ -3315,13 +3315,13 @@
         <v>0</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J53" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>44</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3586</v>
+        <v>3749</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2837</v>
+        <v>2960</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>922</v>
+        <v>996</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>426</v>
+        <v>452</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>577</v>
+        <v>602</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>649</v>
+        <v>686</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>471</v>
+        <v>501</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>107</v>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>520</v>
+        <v>554</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>464</v>
+        <v>494</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L16" s="12" t="n">
         <v>65</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>3</v>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>34</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>11</v>
@@ -1255,19 +1255,19 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>24</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>47</v>
@@ -1276,7 +1276,7 @@
         <v>30</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>45</v>
@@ -1314,22 +1314,22 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L19" s="12" t="n">
         <v>11</v>
@@ -1349,118 +1349,118 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06905</t>
+          <t>16968</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>RIETI</t>
+          <t>FIUMICINO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>S.S.4 KM.87+602</t>
+          <t>VIA PORTUENSE 2468</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Scagnetti Giampiero</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>16968</t>
+          <t>06905</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>FIUMICINO</t>
+          <t>RIETI</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIA PORTUENSE 2468</t>
+          <t>S.S.4 KM.87+602</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Scagnetti Giampiero</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1491,28 +1491,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>6</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>4</v>
@@ -1550,28 +1550,28 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>18</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>25</v>
@@ -1609,28 +1609,28 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L24" s="12" t="n">
         <v>17</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>0</v>
@@ -1668,19 +1668,19 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>24</v>
@@ -1689,10 +1689,10 @@
         <v>13</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>57176</t>
+          <t>07221</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA KM 12+943, 1423</t>
+          <t>VIA TAGLIAMENTO 0049</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,46 +1723,46 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>68</v>
+        <v>166</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>07221</t>
+          <t>57176</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VIA TAGLIAMENTO 0049</t>
+          <t>VIA CASILINA KM 12+943, 1423</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,39 +1782,39 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>159</v>
+        <v>70</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1845,35 +1845,35 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>9</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L28" s="12" t="n">
         <v>24</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1904,19 +1904,19 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>11</v>
@@ -1925,7 +1925,7 @@
         <v>17</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>0</v>
@@ -1966,13 +1966,13 @@
         <v>61</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>57</v>
@@ -1984,14 +1984,14 @@
         <v>2</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>2</v>
@@ -2034,16 +2034,16 @@
         <v>10</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>0</v>
@@ -2081,28 +2081,28 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>8</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>11</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>0</v>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>8</v>
@@ -2152,78 +2152,78 @@
         <v>4</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L33" s="12" t="n">
         <v>11</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>36942</t>
+          <t>58258</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>CASTEL GANDOLFO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA MAREMMANA KM 26, 150</t>
+          <t>VIA NOMENTANA, 850</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Manzo Fabio</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>59</v>
+        <v>106</v>
       </c>
       <c r="H34" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="J34" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="K34" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L34" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M34" s="12" t="n">
+        <v>187</v>
+      </c>
+      <c r="N34" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="I34" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="J34" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="K34" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L34" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="M34" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="N34" s="12" t="n">
-        <v>6</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2234,55 +2234,55 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>58258</t>
+          <t>36942</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CASTEL GANDOLFO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIA NOMENTANA, 850</t>
+          <t>VIA MAREMMANA KM 26, 150</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Manzo Fabio</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I35" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J35" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="J35" s="12" t="n">
-        <v>38</v>
-      </c>
       <c r="K35" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L35" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="M35" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="N35" s="12" t="n">
         <v>6</v>
-      </c>
-      <c r="M35" s="12" t="n">
-        <v>180</v>
-      </c>
-      <c r="N35" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2317,42 +2317,42 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L36" s="12" t="n">
         <v>3</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>58342</t>
+          <t>07143</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2362,56 +2362,56 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>VIA GROTTA PERFETTA 546</t>
+          <t>VIA AURELIA KM 8,456</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Manzo Fabio</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>07143</t>
+          <t>58342</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2421,42 +2421,42 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA AURELIA KM 8,456</t>
+          <t>VIA GROTTA PERFETTA 546</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Manzo Fabio</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
         <v>37</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="H38" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I38" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J38" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="K38" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L38" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I38" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="K38" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="L38" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="M38" s="12" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>1</v>
@@ -2494,13 +2494,13 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" s="12" t="n">
         <v>5</v>
@@ -2512,10 +2512,10 @@
         <v>11</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>0</v>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>1</v>
@@ -2565,16 +2565,16 @@
         <v>7</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>9</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>1</v>
@@ -2588,17 +2588,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>55811</t>
+          <t>55307</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>POMEZIA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>VIA PONTINA KM 31+384</t>
+          <t>VIA CASILINA, 930</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2608,46 +2608,46 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="K41" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L41" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M41" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="N41" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J41" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="K41" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="L41" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="M41" s="12" t="n">
-        <v>65</v>
-      </c>
-      <c r="N41" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>55307</t>
+          <t>58264</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2657,12 +2657,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA, 930</t>
+          <t>VIA CIAMPINO KM. 0+370 CAPANNELLE</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Manzo Fabio</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2671,52 +2671,52 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L42" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M42" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="N42" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="M42" s="12" t="n">
-        <v>64</v>
-      </c>
-      <c r="N42" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>27100</t>
+          <t>55811</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>POMEZIA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA  110 110</t>
+          <t>VIA PONTINA KM 31+384</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2726,46 +2726,46 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>58264</t>
+          <t>27100</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>VIA CIAMPINO KM. 0+370 CAPANNELLE</t>
+          <t>VIA CASILINA  110 110</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Manzo Fabio</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2789,35 +2789,35 @@
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2851,13 +2851,13 @@
         <v>23</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H45" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J45" s="12" t="n">
         <v>15</v>
@@ -2869,14 +2869,14 @@
         <v>7</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="N45" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2907,28 +2907,28 @@
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>0</v>
@@ -2987,7 +2987,7 @@
         <v>0</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N47" s="12" t="n">
         <v>1</v>
@@ -3028,7 +3028,7 @@
         <v>9</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" s="12" t="n">
         <v>2</v>
@@ -3046,14 +3046,14 @@
         <v>3</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="N48" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3083,7 @@
         <v>9</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H49" s="12" t="n">
         <v>0</v>
@@ -3260,7 +3260,7 @@
         <v>2</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H52" s="12" t="n">
         <v>0</v>
@@ -3315,7 +3315,7 @@
         <v>0</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H53" s="12" t="n">
         <v>0</v>
@@ -3370,7 +3370,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H54" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O54" headerRowCount="1">
-  <autoFilter ref="A10:O54"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O55" headerRowCount="1">
+  <autoFilter ref="A10:O55"/>
   <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O54"/>
+  <dimension ref="A1:O55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -681,16 +681,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3749</v>
+        <v>3975</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2960</v>
+        <v>3148</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>996</v>
+        <v>1090</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>452</v>
+        <v>475</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>602</v>
+        <v>634</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>686</v>
+        <v>730</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>501</v>
+        <v>535</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>290</v>
+        <v>309</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>437</v>
+        <v>454</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>297</v>
+        <v>322</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>231</v>
+        <v>255</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>554</v>
+        <v>587</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>494</v>
+        <v>517</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>278</v>
+        <v>303</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>249</v>
+        <v>275</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>17</v>
@@ -1090,19 +1090,19 @@
         <v>17</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>36</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>3</v>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,28 +1255,28 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>45</v>
@@ -1290,17 +1290,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07473</t>
+          <t>16968</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>MONTEFIASCONE</t>
+          <t>FIUMICINO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>SS 2 CASSIA KM 97+800</t>
+          <t>VIA PORTUENSE 2468</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,56 +1310,56 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>36</v>
+        <v>140</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>16968</t>
+          <t>07473</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>FIUMICINO</t>
+          <t>MONTEFIASCONE</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIA PORTUENSE 2468</t>
+          <t>SS 2 CASSIA KM 97+800</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,39 +1369,39 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="I20" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="J20" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="K20" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="L20" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="M20" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="J20" s="12" t="n">
-        <v>92</v>
-      </c>
-      <c r="K20" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="L20" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="M20" s="12" t="n">
-        <v>132</v>
-      </c>
       <c r="N20" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1432,31 +1432,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,28 +1491,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>32</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>47</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>4</v>
@@ -1550,28 +1550,28 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>45</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>25</v>
@@ -1609,31 +1609,31 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>55</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1668,31 +1668,31 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
+        <v>93</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>121</v>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="I25" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="J25" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="G25" s="12" t="n">
-        <v>112</v>
-      </c>
-      <c r="H25" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="I25" s="12" t="n">
-        <v>58</v>
-      </c>
-      <c r="J25" s="12" t="n">
-        <v>78</v>
-      </c>
       <c r="K25" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,19 +1786,19 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>17</v>
@@ -1807,31 +1807,31 @@
         <v>12</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>12</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>54638</t>
+          <t>07224</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>VITERBO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>TANGENZIALE OVEST N 15</t>
+          <t>CIRCONVALLAZIONE GIANICOLENSE 340</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,56 +1841,56 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>86</v>
+      </c>
+      <c r="H28" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="G28" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="H28" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="I28" s="12" t="n">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>136</v>
+        <v>62</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>27224</t>
+          <t>54638</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CAMPAGNANO DI ROMA</t>
+          <t>VITERBO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>SS 2 CASSIA BIS KM30</t>
+          <t>TANGENZIALE OVEST N 15</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,56 +1900,56 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>95</v>
+        <v>58</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>76</v>
+        <v>141</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07224</t>
+          <t>27224</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CAMPAGNANO DI ROMA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>CIRCONVALLAZIONE GIANICOLENSE 340</t>
+          <t>SS 2 CASSIA BIS KM30</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,35 +1959,35 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2022,28 +2022,28 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>0</v>
@@ -2057,17 +2057,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>59331</t>
+          <t>07181</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>MONTALTO DI CASTRO</t>
+          <t>SUBIACO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>S.S. 1 AURELIA SUD KM 107+200</t>
+          <t>SUBLACENSE KM 72*883</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,20 +2077,20 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J32" s="12" t="n">
         <v>41</v>
@@ -2102,31 +2102,31 @@
         <v>11</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>07181</t>
+          <t>59331</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SUBIACO</t>
+          <t>MONTALTO DI CASTRO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>SUBLACENSE KM 72*883</t>
+          <t>S.S. 1 AURELIA SUD KM 107+200</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,46 +2136,46 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>58258</t>
+          <t>36953</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA NOMENTANA, 850</t>
+          <t>VIA ELSA DE GIORGI</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2199,35 +2199,35 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="H34" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="I34" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="J34" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="K34" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="L34" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I34" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="J34" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="K34" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="L34" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="M34" s="12" t="n">
-        <v>187</v>
+        <v>213</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2258,19 +2258,19 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I35" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>9</v>
@@ -2279,7 +2279,7 @@
         <v>22</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>6</v>
@@ -2293,7 +2293,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>36953</t>
+          <t>58258</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>VIA ELSA DE GIORGI</t>
+          <t>VIA NOMENTANA, 850</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2317,35 +2317,35 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>6</v>
@@ -2388,16 +2388,16 @@
         <v>1</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L37" s="12" t="n">
         <v>9</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>1</v>
@@ -2411,125 +2411,125 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>58342</t>
+          <t>58351</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>VALMONTONE</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA GROTTA PERFETTA 546</t>
+          <t>VIA CASILINA KM 41</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Funari Emanuele</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="H38" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I38" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="J38" s="12" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>58351</t>
+          <t>55811</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>VALMONTONE</t>
+          <t>POMEZIA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA KM 41</t>
+          <t>VIA PONTINA KM 31+384</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Funari Emanuele</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="H39" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>36981</t>
+          <t>58342</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>VIA COLLATINA 427, ANG. VIA PETITTI</t>
+          <t>VIA GROTTA PERFETTA 546</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>1</v>
@@ -2588,7 +2588,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>55307</t>
+          <t>36981</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA, 930</t>
+          <t>VIA COLLATINA 427, ANG. VIA PETITTI</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2612,35 +2612,35 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>67</v>
+        <v>142</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2671,19 +2671,19 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K42" s="12" t="n">
         <v>10</v>
@@ -2692,7 +2692,7 @@
         <v>6</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="N42" s="12" t="n">
         <v>3</v>
@@ -2706,17 +2706,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>55811</t>
+          <t>55307</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>POMEZIA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>VIA PONTINA KM 31+384</t>
+          <t>VIA CASILINA, 930</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2726,35 +2726,35 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H43" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>68</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2789,28 +2789,28 @@
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L44" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="N44" s="12" t="n">
         <v>22</v>
@@ -2848,31 +2848,31 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L45" s="12" t="n">
         <v>7</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2910,13 +2910,13 @@
         <v>19</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="H46" s="12" t="n">
         <v>19</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J46" s="12" t="n">
         <v>27</v>
@@ -2928,7 +2928,7 @@
         <v>0</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>0</v>
@@ -2966,22 +2966,22 @@
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L47" s="12" t="n">
         <v>0</v>
@@ -3028,7 +3028,7 @@
         <v>9</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H48" s="12" t="n">
         <v>2</v>
@@ -3046,14 +3046,14 @@
         <v>3</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N48" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3083,7 @@
         <v>9</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H49" s="12" t="n">
         <v>0</v>
@@ -3260,7 +3260,7 @@
         <v>2</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H52" s="12" t="n">
         <v>0</v>
@@ -3285,14 +3285,14 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>27183</t>
+          <t>54315</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>V. DON P. BORGHI ANG.JACH</t>
+          <t>V.LE OCEANO PACIFICO</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
@@ -3312,22 +3312,22 @@
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="12" t="n">
         <v>0</v>
@@ -3340,14 +3340,14 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>36961</t>
+          <t>27183</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -3357,43 +3357,98 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>S.P. 493 BRACCIANESE KM.11,500</t>
+          <t>V. DON P. BORGHI ANG.JACH</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="2" t="inlineStr">
         <is>
+          <t>GIOVANNINI DANIELE</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="H54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="J54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>36961</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>ROMA</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>S.P. 493 BRACCIANESE KM.11,500</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr"/>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
           <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
-      <c r="F54" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="H54" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="12" t="n">
+      <c r="F55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="H55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="J54" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="2" t="inlineStr">
+      <c r="J55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>

--- a/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>45</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3975</v>
+        <v>4155</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3148</v>
+        <v>3301</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1090</v>
+        <v>1179</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>475</v>
+        <v>495</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>634</v>
+        <v>660</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>730</v>
+        <v>768</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>535</v>
+        <v>554</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>81</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>454</v>
+        <v>475</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>109</v>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>65</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>587</v>
+        <v>610</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>517</v>
+        <v>536</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>8</v>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>17</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>36</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L16" s="12" t="n">
         <v>68</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>25</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>14</v>
@@ -1255,28 +1255,28 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G18" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="H18" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="I18" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="J18" s="12" t="n">
+        <v>108</v>
+      </c>
+      <c r="K18" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="H18" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="I18" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="J18" s="12" t="n">
-        <v>105</v>
-      </c>
-      <c r="K18" s="12" t="n">
-        <v>52</v>
-      </c>
       <c r="L18" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>45</v>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>2</v>
@@ -1373,28 +1373,28 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>12</v>
@@ -1432,35 +1432,35 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>125</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1491,28 +1491,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>32</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>47</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>4</v>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>16</v>
@@ -1562,16 +1562,16 @@
         <v>45</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>19</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>25</v>
@@ -1609,28 +1609,28 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L24" s="12" t="n">
         <v>18</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>1</v>
@@ -1668,28 +1668,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>14</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>9</v>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>31</v>
@@ -1748,7 +1748,7 @@
         <v>15</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>6</v>
@@ -1786,35 +1786,35 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>12</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1845,31 +1845,31 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L28" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>7</v>
@@ -1916,7 +1916,7 @@
         <v>10</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>14</v>
@@ -1925,7 +1925,7 @@
         <v>24</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>6</v>
@@ -1963,19 +1963,19 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>11</v>
@@ -1984,7 +1984,7 @@
         <v>19</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>0</v>
@@ -2025,25 +2025,25 @@
         <v>62</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J31" s="12" t="n">
         <v>46</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>0</v>
@@ -2081,28 +2081,28 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>4</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>11</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>3</v>
@@ -2140,149 +2140,149 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>84</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>9</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L33" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>36953</t>
+          <t>36942</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CASTEL GANDOLFO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA ELSA DE GIORGI</t>
+          <t>VIA MAREMMANA KM 26, 150</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Manzo Fabio</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>213</v>
+        <v>61</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>36942</t>
+          <t>58258</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>CASTEL GANDOLFO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIA MAREMMANA KM 26, 150</t>
+          <t>VIA NOMENTANA, 850</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Manzo Fabio</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>67</v>
+        <v>121</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>52</v>
+        <v>195</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>58258</t>
+          <t>36953</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>VIA NOMENTANA, 850</t>
+          <t>VIA ELSA DE GIORGI</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2317,35 +2317,35 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>116</v>
+        <v>55</v>
       </c>
       <c r="H36" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="I36" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="J36" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="K36" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="L36" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I36" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="J36" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="K36" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="L36" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="M36" s="12" t="n">
-        <v>187</v>
+        <v>222</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>6</v>
@@ -2388,16 +2388,16 @@
         <v>1</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>1</v>
@@ -2411,76 +2411,76 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>58351</t>
+          <t>55811</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>VALMONTONE</t>
+          <t>POMEZIA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA KM 41</t>
+          <t>VIA PONTINA KM 31+384</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Funari Emanuele</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>55811</t>
+          <t>58342</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>POMEZIA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA PONTINA KM 31+384</t>
+          <t>VIA GROTTA PERFETTA 546</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2494,31 +2494,31 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2529,55 +2529,55 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>58342</t>
+          <t>58351</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>VALMONTONE</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>VIA GROTTA PERFETTA 546</t>
+          <t>VIA CASILINA KM 41</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Funari Emanuele</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="H40" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I40" s="12" t="n">
-        <v>16</v>
-      </c>
       <c r="J40" s="12" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>36981</t>
+          <t>27100</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>VIA COLLATINA 427, ANG. VIA PETITTI</t>
+          <t>VIA CASILINA  110 110</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2612,35 +2612,35 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="I41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="K41" s="12" t="n">
         <v>8</v>
-      </c>
-      <c r="J41" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="K41" s="12" t="n">
-        <v>9</v>
       </c>
       <c r="L41" s="12" t="n">
         <v>5</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>142</v>
+        <v>63</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2671,28 +2671,28 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L42" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N42" s="12" t="n">
         <v>3</v>
@@ -2730,42 +2730,42 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L43" s="12" t="n">
         <v>3</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="N43" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>27100</t>
+          <t>36981</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA  110 110</t>
+          <t>VIA COLLATINA 427, ANG. VIA PETITTI</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2789,35 +2789,35 @@
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L44" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M44" s="12" t="n">
+        <v>151</v>
+      </c>
+      <c r="N44" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="M44" s="12" t="n">
-        <v>59</v>
-      </c>
-      <c r="N44" s="12" t="n">
-        <v>22</v>
-      </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2848,35 +2848,35 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I45" s="12" t="n">
         <v>17</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L45" s="12" t="n">
         <v>7</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2907,19 +2907,19 @@
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="H46" s="12" t="n">
         <v>19</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>8</v>
@@ -2928,7 +2928,7 @@
         <v>0</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>0</v>
@@ -2966,35 +2966,35 @@
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N47" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3025,10 +3025,10 @@
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H48" s="12" t="n">
         <v>2</v>
@@ -3037,16 +3037,16 @@
         <v>0</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L48" s="12" t="n">
         <v>3</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N48" s="12" t="n">
         <v>2</v>
@@ -3060,131 +3060,131 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>57171</t>
+          <t>58341</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>LADISPOLI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>VIA PALO LAZIALE 8</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr"/>
+          <t>VIA ARDEATINA</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
         <v>9</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="N49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>07164</t>
+          <t>57171</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>CASTEL GANDOLFO</t>
+          <t>LADISPOLI</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>VIA APPIA KM 24,600 SNC 0012</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+          <t>VIA PALO LAZIALE 8</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr"/>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
         <v>9</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="H50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K50" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>58341</t>
+          <t>07164</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CASTEL GANDOLFO</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>VIA ARDEATINA</t>
+          <t>VIA APPIA KM 24,600 SNC 0012</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3198,7 +3198,7 @@
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G51" s="12" t="n">
         <v>0</v>
@@ -3210,19 +3210,19 @@
         <v>0</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         <v>2</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H52" s="12" t="n">
         <v>0</v>
@@ -3333,14 +3333,14 @@
         <v>0</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H54" s="12" t="n">
         <v>0</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H55" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>45</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4155</v>
+        <v>4395</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3301</v>
+        <v>3500</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1179</v>
+        <v>1298</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>495</v>
+        <v>515</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>660</v>
+        <v>687</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>768</v>
+        <v>806</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>405</v>
+        <v>420</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>554</v>
+        <v>576</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>475</v>
+        <v>499</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,153 +960,153 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>331</v>
+        <v>375</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>65</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>264</v>
+        <v>294</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>610</v>
+        <v>646</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>536</v>
+        <v>567</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>07081</t>
+          <t>07171</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>COLLEFERRO</t>
+          <t>CIVITAVECCHIA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>CASILINA,  0928</t>
+          <t>S.S. AURELIA KM 68+885</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Funari Emanuele</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>318</v>
+        <v>259</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>140</v>
+        <v>21</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>288</v>
+        <v>17</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>252</v>
+        <v>343</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>07171</t>
+          <t>07081</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CIVITAVECCHIA</t>
+          <t>COLLEFERRO</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>S.S. AURELIA KM 68+885</t>
+          <t>CASILINA,  0928</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Funari Emanuele</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>250</v>
+        <v>330</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>19</v>
+        <v>145</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>17</v>
+        <v>303</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>330</v>
+        <v>267</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>36</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>30</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>25</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,28 +1255,28 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>54</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>26</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>33</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>45</v>
@@ -1290,17 +1290,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>16968</t>
+          <t>07473</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>FIUMICINO</t>
+          <t>MONTEFIASCONE</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>VIA PORTUENSE 2468</t>
+          <t>SS 2 CASSIA KM 97+800</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,56 +1310,56 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>159</v>
+        <v>125</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>147</v>
+        <v>41</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>07473</t>
+          <t>16968</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>MONTEFIASCONE</t>
+          <t>FIUMICINO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>SS 2 CASSIA KM 97+800</t>
+          <t>VIA PORTUENSE 2468</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,39 +1369,39 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>88</v>
+        <v>45</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1432,35 +1432,35 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>35</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1550,28 +1550,28 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>16</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>19</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>25</v>
@@ -1609,28 +1609,28 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>344</v>
+        <v>360</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>1</v>
@@ -1668,28 +1668,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>14</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>9</v>
@@ -1727,28 +1727,28 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="I26" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="J26" s="12" t="n">
+        <v>96</v>
+      </c>
+      <c r="K26" s="12" t="n">
         <v>42</v>
-      </c>
-      <c r="J26" s="12" t="n">
-        <v>75</v>
-      </c>
-      <c r="K26" s="12" t="n">
-        <v>31</v>
       </c>
       <c r="L26" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>6</v>
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>12</v>
@@ -1845,31 +1845,31 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
+        <v>87</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>97</v>
+      </c>
+      <c r="H28" s="12" t="n">
+        <v>85</v>
+      </c>
+      <c r="I28" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="J28" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="G28" s="12" t="n">
-        <v>93</v>
-      </c>
-      <c r="H28" s="12" t="n">
-        <v>78</v>
-      </c>
-      <c r="I28" s="12" t="n">
-        <v>77</v>
-      </c>
-      <c r="J28" s="12" t="n">
-        <v>79</v>
-      </c>
       <c r="K28" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L28" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1904,35 +1904,35 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L29" s="12" t="n">
         <v>24</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1966,13 +1966,13 @@
         <v>71</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>42</v>
@@ -1984,7 +1984,7 @@
         <v>19</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>0</v>
@@ -1998,232 +1998,232 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>07132</t>
+          <t>07181</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>MARINO</t>
+          <t>SUBIACO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>APPIA NUOVA KM 18+934 0006</t>
+          <t>SUBLACENSE KM 72*883</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Manzo Fabio</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="H31" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="I31" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J31" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="K31" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="L31" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="M31" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="N31" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I31" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="J31" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="K31" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="L31" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="M31" s="12" t="n">
-        <v>84</v>
-      </c>
-      <c r="N31" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>07181</t>
+          <t>07132</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SUBIACO</t>
+          <t>MARINO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>SUBLACENSE KM 72*883</t>
+          <t>APPIA NUOVA KM 18+934 0006</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Manzo Fabio</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G32" s="12" t="n">
+        <v>116</v>
+      </c>
+      <c r="H32" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="J32" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="H32" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="I32" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J32" s="12" t="n">
-        <v>48</v>
-      </c>
       <c r="K32" s="12" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>59331</t>
+          <t>36942</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>MONTALTO DI CASTRO</t>
+          <t>CASTEL GANDOLFO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>S.S. 1 AURELIA SUD KM 107+200</t>
+          <t>VIA MAREMMANA KM 26, 150</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Manzo Fabio</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>36942</t>
+          <t>59331</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>CASTEL GANDOLFO</t>
+          <t>MONTALTO DI CASTRO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA MAREMMANA KM 26, 150</t>
+          <t>S.S. 1 AURELIA SUD KM 107+200</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Manzo Fabio</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I34" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>61</v>
+        <v>102</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>58258</t>
+          <t>36953</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIA NOMENTANA, 850</t>
+          <t>VIA ELSA DE GIORGI</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2261,39 +2261,39 @@
         <v>52</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>121</v>
+        <v>58</v>
       </c>
       <c r="H35" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="I35" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="J35" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="K35" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="L35" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I35" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="J35" s="12" t="n">
-        <v>44</v>
-      </c>
-      <c r="K35" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="L35" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="M35" s="12" t="n">
-        <v>195</v>
+        <v>228</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>36953</t>
+          <t>58258</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>VIA ELSA DE GIORGI</t>
+          <t>VIA NOMENTANA, 850</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2317,35 +2317,35 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>55</v>
+        <v>131</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2376,28 +2376,28 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I37" s="12" t="n">
         <v>1</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L37" s="12" t="n">
         <v>11</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>1</v>
@@ -2411,17 +2411,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>55811</t>
+          <t>58342</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>POMEZIA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA PONTINA KM 31+384</t>
+          <t>VIA GROTTA PERFETTA 546</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2435,31 +2435,31 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2470,17 +2470,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>58342</t>
+          <t>55811</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>POMEZIA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA GROTTA PERFETTA 546</t>
+          <t>VIA PONTINA KM 31+384</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2494,31 +2494,31 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2529,125 +2529,125 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>58351</t>
+          <t>55307</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>VALMONTONE</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA KM 41</t>
+          <t>VIA CASILINA, 930</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Funari Emanuele</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
         <v>41</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>27100</t>
+          <t>58351</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>VALMONTONE</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA  110 110</t>
+          <t>VIA CASILINA KM 41</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Funari Emanuele</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>63</v>
+        <v>109</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>58264</t>
+          <t>27100</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2657,12 +2657,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>VIA CIAMPINO KM. 0+370 CAPANNELLE</t>
+          <t>VIA CASILINA  110 110</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Manzo Fabio</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2671,42 +2671,42 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="I42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="G42" s="12" t="n">
-        <v>74</v>
-      </c>
-      <c r="H42" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="I42" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="J42" s="12" t="n">
-        <v>28</v>
-      </c>
       <c r="K42" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>55307</t>
+          <t>58264</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA, 930</t>
+          <t>VIA CIAMPINO KM. 0+370 CAPANNELLE</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Manzo Fabio</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2730,35 +2730,35 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L43" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M43" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="N43" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="M43" s="12" t="n">
-        <v>71</v>
-      </c>
-      <c r="N43" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
         <v>33</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H44" s="12" t="n">
         <v>1</v>
@@ -2810,7 +2810,7 @@
         <v>5</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="N44" s="12" t="n">
         <v>1</v>
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H45" s="12" t="n">
         <v>13</v>
@@ -2860,16 +2860,16 @@
         <v>17</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L45" s="12" t="n">
         <v>7</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="N45" s="12" t="n">
         <v>6</v>
@@ -2907,31 +2907,31 @@
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2966,19 +2966,19 @@
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>6</v>
@@ -3028,7 +3028,7 @@
         <v>10</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H48" s="12" t="n">
         <v>2</v>
@@ -3046,14 +3046,14 @@
         <v>3</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N48" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
         <v>9</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H50" s="12" t="n">
         <v>0</v>
@@ -3260,7 +3260,7 @@
         <v>2</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H52" s="12" t="n">
         <v>0</v>
@@ -3333,14 +3333,14 @@
         <v>0</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3370,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="H54" s="12" t="n">
         <v>0</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H55" s="12" t="n">
         <v>0</v>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>45</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4395</v>
+        <v>4669</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3500</v>
+        <v>3718</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1298</v>
+        <v>1431</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>515</v>
+        <v>547</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>687</v>
+        <v>722</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>387</v>
+        <v>418</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>806</v>
+        <v>856</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>576</v>
+        <v>598</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>338</v>
+        <v>367</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>499</v>
+        <v>526</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,153 +960,153 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>375</v>
+        <v>404</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>367</v>
+        <v>401</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>294</v>
+        <v>321</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>646</v>
+        <v>677</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>567</v>
+        <v>588</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>07171</t>
+          <t>07081</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CIVITAVECCHIA</t>
+          <t>COLLEFERRO</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>S.S. AURELIA KM 68+885</t>
+          <t>CASILINA,  0928</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Funari Emanuele</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>259</v>
+        <v>345</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>21</v>
+        <v>158</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>17</v>
+        <v>321</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>343</v>
+        <v>284</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>07081</t>
+          <t>07171</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>COLLEFERRO</t>
+          <t>CIVITAVECCHIA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>CASILINA,  0928</t>
+          <t>S.S. AURELIA KM 68+885</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Funari Emanuele</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>330</v>
+        <v>269</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>145</v>
+        <v>23</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>303</v>
+        <v>17</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>267</v>
+        <v>371</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>56</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>330</v>
+        <v>349</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>5</v>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>15</v>
@@ -1255,52 +1255,52 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>45</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07473</t>
+          <t>16968</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>MONTEFIASCONE</t>
+          <t>FIUMICINO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>SS 2 CASSIA KM 97+800</t>
+          <t>VIA PORTUENSE 2468</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,56 +1310,56 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>125</v>
+        <v>182</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>91</v>
+        <v>49</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>41</v>
+        <v>161</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>16968</t>
+          <t>07473</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>FIUMICINO</t>
+          <t>MONTEFIASCONE</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIA PORTUENSE 2468</t>
+          <t>SS 2 CASSIA KM 97+800</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,94 +1369,94 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>166</v>
+        <v>128</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>45</v>
+        <v>93</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>150</v>
+        <v>41</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06905</t>
+          <t>17111</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>RIETI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>S.S.4 KM.87+602</t>
+          <t>SS SALARIA KM 14, 895 EST</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Scagnetti Giampiero</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>128</v>
+        <v>214</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1467,55 +1467,55 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>17111</t>
+          <t>06905</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>RIETI</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>SS SALARIA KM 14, 895 EST</t>
+          <t>S.S.4 KM.87+602</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Scagnetti Giampiero</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>113</v>
+        <v>136</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>207</v>
+        <v>129</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1550,31 +1550,31 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>46</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>19</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1609,19 +1609,19 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>32</v>
@@ -1630,7 +1630,7 @@
         <v>23</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>1</v>
@@ -1668,28 +1668,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>9</v>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I26" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="J26" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="K26" s="12" t="n">
         <v>45</v>
-      </c>
-      <c r="J26" s="12" t="n">
-        <v>96</v>
-      </c>
-      <c r="K26" s="12" t="n">
-        <v>42</v>
       </c>
       <c r="L26" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>57176</t>
+          <t>07224</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA KM 12+943, 1423</t>
+          <t>CIRCONVALLAZIONE GIANICOLENSE 340</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,35 +1782,35 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>07224</t>
+          <t>57176</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>CIRCONVALLAZIONE GIANICOLENSE 340</t>
+          <t>VIA CASILINA KM 12+943, 1423</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,39 +1841,39 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>81</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>9</v>
@@ -1916,40 +1916,40 @@
         <v>12</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>16</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>27224</t>
+          <t>07181</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>CAMPAGNANO DI ROMA</t>
+          <t>SUBIACO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>SS 2 CASSIA BIS KM30</t>
+          <t>SUBLACENSE KM 72*883</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,56 +1959,56 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="H30" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="I30" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J30" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="K30" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="L30" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="M30" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="N30" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I30" s="12" t="n">
-        <v>45</v>
-      </c>
-      <c r="J30" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="K30" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="L30" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="M30" s="12" t="n">
-        <v>84</v>
-      </c>
-      <c r="N30" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>07181</t>
+          <t>27224</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>SUBIACO</t>
+          <t>CAMPAGNANO DI ROMA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>SUBLACENSE KM 72*883</t>
+          <t>SS 2 CASSIA BIS KM30</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2018,39 +2018,39 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2081,28 +2081,28 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>0</v>
@@ -2140,52 +2140,52 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>11</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>10</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>59331</t>
+          <t>36953</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>MONTALTO DI CASTRO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>S.S. 1 AURELIA SUD KM 107+200</t>
+          <t>VIA ELSA DE GIORGI</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,56 +2195,56 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>102</v>
+        <v>250</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>36953</t>
+          <t>59331</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MONTALTO DI CASTRO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIA ELSA DE GIORGI</t>
+          <t>S.S. 1 AURELIA SUD KM 107+200</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,46 +2254,46 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>228</v>
+        <v>105</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>58258</t>
+          <t>07143</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2303,56 +2303,56 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>VIA NOMENTANA, 850</t>
+          <t>VIA AURELIA KM 8,456</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Manzo Fabio</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>131</v>
+        <v>42</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>205</v>
+        <v>154</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>07143</t>
+          <t>58258</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2362,49 +2362,49 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>VIA AURELIA KM 8,456</t>
+          <t>VIA NOMENTANA, 850</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Manzo Fabio</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G37" s="12" t="n">
+        <v>144</v>
+      </c>
+      <c r="H37" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I37" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="H37" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="I37" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="J37" s="12" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>147</v>
+        <v>218</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2435,28 +2435,28 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I38" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="J38" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="K38" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="J38" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="K38" s="12" t="n">
-        <v>15</v>
-      </c>
       <c r="L38" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>7</v>
@@ -2470,66 +2470,66 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>55811</t>
+          <t>58351</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>POMEZIA</t>
+          <t>VALMONTONE</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA PONTINA KM 31+384</t>
+          <t>VIA CASILINA KM 41</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Funari Emanuele</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>55307</t>
+          <t>27100</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA, 930</t>
+          <t>VIA CASILINA  110 110</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2553,31 +2553,31 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="I40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="K40" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L40" s="12" t="n">
         <v>6</v>
-      </c>
-      <c r="I40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="K40" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="L40" s="12" t="n">
-        <v>3</v>
       </c>
       <c r="M40" s="12" t="n">
         <v>74</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2588,66 +2588,66 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>58351</t>
+          <t>55811</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>VALMONTONE</t>
+          <t>POMEZIA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA KM 41</t>
+          <t>VIA PONTINA KM 31+384</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Funari Emanuele</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>27100</t>
+          <t>55307</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA  110 110</t>
+          <t>VIA CASILINA, 930</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2671,31 +2671,31 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2730,31 +2730,31 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I43" s="12" t="n">
         <v>26</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L43" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2792,13 +2792,13 @@
         <v>33</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J44" s="12" t="n">
         <v>33</v>
@@ -2810,7 +2810,7 @@
         <v>5</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="N44" s="12" t="n">
         <v>1</v>
@@ -2848,28 +2848,28 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="N45" s="12" t="n">
         <v>6</v>
@@ -2910,13 +2910,13 @@
         <v>22</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J46" s="12" t="n">
         <v>30</v>
@@ -2928,10 +2928,10 @@
         <v>0</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G47" s="12" t="n">
         <v>0</v>
@@ -2978,7 +2978,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>6</v>
@@ -2987,14 +2987,14 @@
         <v>0</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N47" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3028,13 +3028,13 @@
         <v>10</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H48" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" s="12" t="n">
         <v>9</v>
@@ -3046,14 +3046,14 @@
         <v>3</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N48" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
         <v>9</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H50" s="12" t="n">
         <v>0</v>
@@ -3260,7 +3260,7 @@
         <v>2</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H52" s="12" t="n">
         <v>0</v>
@@ -3318,7 +3318,7 @@
         <v>0</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I53" s="12" t="n">
         <v>0</v>
@@ -3333,7 +3333,7 @@
         <v>0</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N53" s="12" t="n">
         <v>0</v>
@@ -3370,13 +3370,13 @@
         <v>0</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="H54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J54" s="12" t="n">
         <v>0</v>
@@ -3425,13 +3425,13 @@
         <v>0</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J55" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>45</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4669</v>
+        <v>4947</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3718</v>
+        <v>3938</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1431</v>
+        <v>1564</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>547</v>
+        <v>569</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>722</v>
+        <v>752</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>418</v>
+        <v>437</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>856</v>
+        <v>908</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>598</v>
+        <v>611</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>526</v>
+        <v>569</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>113</v>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>404</v>
+        <v>428</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>401</v>
+        <v>424</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>677</v>
+        <v>706</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>588</v>
+        <v>609</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="G14" s="12" t="n">
+        <v>362</v>
+      </c>
+      <c r="H14" s="12" t="n">
+        <v>167</v>
+      </c>
+      <c r="I14" s="12" t="n">
         <v>345</v>
       </c>
-      <c r="H14" s="12" t="n">
-        <v>158</v>
-      </c>
-      <c r="I14" s="12" t="n">
-        <v>321</v>
-      </c>
       <c r="J14" s="12" t="n">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>9</v>
@@ -1078,31 +1078,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>371</v>
+        <v>399</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,28 +1137,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>32</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>5</v>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>15</v>
@@ -1255,28 +1255,28 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>34</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>45</v>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L19" s="12" t="n">
         <v>25</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>2</v>
@@ -1349,17 +1349,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>07473</t>
+          <t>17111</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>MONTEFIASCONE</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>SS 2 CASSIA KM 97+800</t>
+          <t>SS SALARIA KM 14, 895 EST</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>128</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>41</v>
+        <v>230</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>12</v>
@@ -1408,17 +1408,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>17111</t>
+          <t>07473</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MONTEFIASCONE</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>SS SALARIA KM 14, 895 EST</t>
+          <t>SS 2 CASSIA KM 97+800</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,35 +1428,35 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>37</v>
+        <v>95</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>214</v>
+        <v>48</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1467,177 +1467,177 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>06905</t>
+          <t>56322</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>RIETI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>S.S.4 KM.87+602</t>
+          <t>VIA AURELIA 711</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Scagnetti Giampiero</t>
+          <t>Manzo Fabio</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>136</v>
+        <v>293</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>129</v>
+        <v>335</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>56322</t>
+          <t>06905</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>RIETI</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA AURELIA 711</t>
+          <t>S.S.4 KM.87+602</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Manzo Fabio</t>
+          <t>Scagnetti Giampiero</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>278</v>
+        <v>142</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>318</v>
+        <v>142</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>07049</t>
+          <t>57176</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>FRASCATI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIA VITTORIO VENETO 34</t>
+          <t>VIA CASILINA KM 12+943, 1423</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Manzo Fabio</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>234</v>
+        <v>0</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>23</v>
+        <v>116</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>375</v>
+        <v>86</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1668,28 +1668,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>9</v>
@@ -1703,55 +1703,55 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07221</t>
+          <t>07049</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>FRASCATI</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIA TAGLIAMENTO 0049</t>
+          <t>VIA VITTORIO VENETO 34</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Manzo Fabio</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>166</v>
+        <v>245</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="J26" s="12" t="n">
         <v>100</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>201</v>
+        <v>384</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>07224</t>
+          <t>07221</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>CIRCONVALLAZIONE GIANICOLENSE 340</t>
+          <t>VIA TAGLIAMENTO 0049</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,46 +1782,46 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>92</v>
+        <v>217</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>57176</t>
+          <t>07224</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA KM 12+943, 1423</t>
+          <t>CIRCONVALLAZIONE GIANICOLENSE 340</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,35 +1841,35 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1904,19 +1904,19 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>16</v>
@@ -1925,14 +1925,14 @@
         <v>25</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1963,57 +1963,57 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>14</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>27224</t>
+          <t>07132</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CAMPAGNANO DI ROMA</t>
+          <t>MARINO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>SS 2 CASSIA BIS KM30</t>
+          <t>APPIA NUOVA KM 18+934 0006</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Manzo Fabio</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2022,31 +2022,31 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2057,22 +2057,22 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>07132</t>
+          <t>27224</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>MARINO</t>
+          <t>CAMPAGNANO DI ROMA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>APPIA NUOVA KM 18+934 0006</t>
+          <t>SS 2 CASSIA BIS KM30</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Manzo Fabio</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2081,28 +2081,28 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I32" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="J32" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="K32" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L32" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="J32" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="K32" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="L32" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="M32" s="12" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>0</v>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>5</v>
@@ -2152,7 +2152,7 @@
         <v>11</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>10</v>
@@ -2161,14 +2161,14 @@
         <v>23</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>9</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2199,28 +2199,28 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I34" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="J34" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="K34" s="12" t="n">
         <v>27</v>
-      </c>
-      <c r="J34" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="K34" s="12" t="n">
-        <v>26</v>
       </c>
       <c r="L34" s="12" t="n">
         <v>5</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>2</v>
@@ -2258,10 +2258,10 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="H35" s="12" t="n">
         <v>14</v>
@@ -2270,7 +2270,7 @@
         <v>12</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>18</v>
@@ -2279,10 +2279,10 @@
         <v>12</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>07143</t>
+          <t>58342</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2303,45 +2303,45 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>VIA AURELIA KM 8,456</t>
+          <t>VIA GROTTA PERFETTA 546</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Manzo Fabio</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>58258</t>
+          <t>07143</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2362,163 +2362,163 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>VIA NOMENTANA, 850</t>
+          <t>VIA AURELIA KM 8,456</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Manzo Fabio</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>144</v>
+        <v>49</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>218</v>
+        <v>168</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>58342</t>
+          <t>58351</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>VALMONTONE</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA GROTTA PERFETTA 546</t>
+          <t>VIA CASILINA KM 41</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Funari Emanuele</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>58351</t>
+          <t>58258</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>VALMONTONE</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA KM 41</t>
+          <t>VIA NOMENTANA, 850</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Funari Emanuele</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>93</v>
+        <v>153</v>
       </c>
       <c r="H39" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>113</v>
+        <v>231</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2553,35 +2553,35 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>23</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I41" s="12" t="n">
         <v>1</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L41" s="12" t="n">
         <v>23</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>0</v>
@@ -2671,35 +2671,35 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I42" s="12" t="n">
         <v>1</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L42" s="12" t="n">
         <v>3</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="N42" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2730,10 +2730,10 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H43" s="12" t="n">
         <v>11</v>
@@ -2742,16 +2742,16 @@
         <v>26</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L43" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="N43" s="12" t="n">
         <v>4</v>
@@ -2765,7 +2765,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>36981</t>
+          <t>16949</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>VIA COLLATINA 427, ANG. VIA PETITTI</t>
+          <t>VIA DI PONTE GALERIA  SNC - VIA DI PONTE GALERIA SNC</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2785,46 +2785,46 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K44" s="12" t="n">
         <v>9</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>171</v>
+        <v>83</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>16949</t>
+          <t>36981</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>VIA DI PONTE GALERIA  SNC - VIA DI PONTE GALERIA SNC</t>
+          <t>VIA COLLATINA 427, ANG. VIA PETITTI</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2844,39 +2844,39 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>80</v>
+        <v>195</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2907,31 +2907,31 @@
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3028,13 +3028,13 @@
         <v>10</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H48" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J48" s="12" t="n">
         <v>9</v>
@@ -3046,7 +3046,7 @@
         <v>3</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N48" s="12" t="n">
         <v>2</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N49" s="12" t="n">
         <v>0</v>
@@ -3142,7 +3142,7 @@
         <v>9</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H50" s="12" t="n">
         <v>0</v>
@@ -3233,7 +3233,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>06947</t>
+          <t>54315</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -3243,56 +3243,52 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>VIA OSTIENSE 333</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+          <t>V.LE OCEANO PACIFICO</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr"/>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K52" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="G52" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="H52" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J52" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K52" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>54315</t>
+          <t>06947</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3302,45 +3298,49 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>V.LE OCEANO PACIFICO</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr"/>
+          <t>VIA OSTIENSE 333</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
         <v>2</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J53" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="N53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3370,13 +3370,13 @@
         <v>0</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="H54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J54" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - CRISPINO ALESSANDRO.xlsx
@@ -684,13 +684,13 @@
         <v>45</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4947</v>
+        <v>4996</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3938</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1564</v>
+        <v>1548</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>156</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>185</v>
@@ -863,10 +863,10 @@
         <v>134</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>91</v>
@@ -913,7 +913,7 @@
         <v>63</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>377</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>198</v>
@@ -922,10 +922,10 @@
         <v>86</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>342</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>137</v>
@@ -981,10 +981,10 @@
         <v>84</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>706</v>
+        <v>687</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>609</v>
+        <v>592</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1022,16 +1022,16 @@
         <v>272</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>101</v>
@@ -1040,7 +1040,7 @@
         <v>72</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>9</v>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>25</v>
@@ -1090,7 +1090,7 @@
         <v>18</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>64</v>
@@ -1099,7 +1099,7 @@
         <v>74</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>53</v>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>32</v>
@@ -1149,7 +1149,7 @@
         <v>40</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>59</v>
@@ -1158,7 +1158,7 @@
         <v>80</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>5</v>
@@ -1196,19 +1196,19 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>71</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>46</v>
@@ -1217,31 +1217,31 @@
         <v>34</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>15</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>06965</t>
+          <t>16968</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>FIANO ROMANO</t>
+          <t>FIUMICINO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>S.S.4 DIR. KM. 3 + 400</t>
+          <t>VIA PORTUENSE 2468</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1251,56 +1251,56 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
         <v>156</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>60</v>
+        <v>188</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>213</v>
+        <v>166</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>16968</t>
+          <t>17111</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>FIUMICINO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>VIA PORTUENSE 2468</t>
+          <t>SS SALARIA KM 14, 895 EST</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,56 +1310,56 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
         <v>155</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>189</v>
+        <v>120</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>172</v>
+        <v>229</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>17111</t>
+          <t>06965</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>FIANO ROMANO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>SS SALARIA KM 14, 895 EST</t>
+          <t>S.S.4 DIR. KM. 3 + 400</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,39 +1369,39 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
         <v>154</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>128</v>
+        <v>54</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>230</v>
+        <v>209</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1432,19 +1432,19 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>95</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>69</v>
@@ -1453,10 +1453,10 @@
         <v>16</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,19 +1491,19 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>18</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>33</v>
@@ -1512,10 +1512,10 @@
         <v>24</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>44</v>
@@ -1562,7 +1562,7 @@
         <v>6</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>36</v>
@@ -1585,7 +1585,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>57176</t>
+          <t>80008</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA KM 12+943, 1423</t>
+          <t>CORSO FRANCIA</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,94 +1605,94 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>116</v>
+        <v>25</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>86</v>
+        <v>346</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>80008</t>
+          <t>07049</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>FRASCATI</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>CORSO FRANCIA</t>
+          <t>VIA VITTORIO VENETO 34</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Manzo Fabio</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>166</v>
+        <v>241</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>353</v>
+        <v>379</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1703,55 +1703,55 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07049</t>
+          <t>07221</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>FRASCATI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIA VITTORIO VENETO 34</t>
+          <t>VIA TAGLIAMENTO 0049</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Manzo Fabio</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>245</v>
+        <v>169</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>384</v>
+        <v>212</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>07221</t>
+          <t>57176</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VIA TAGLIAMENTO 0049</t>
+          <t>VIA CASILINA KM 12+943, 1423</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,39 +1782,39 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>217</v>
+        <v>86</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>111</v>
@@ -1857,7 +1857,7 @@
         <v>90</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>68</v>
@@ -1866,14 +1866,14 @@
         <v>3</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>70</v>
@@ -1916,7 +1916,7 @@
         <v>13</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>16</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>19</v>
@@ -1975,7 +1975,7 @@
         <v>6</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>27</v>
@@ -1984,10 +1984,10 @@
         <v>14</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>23</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>22</v>
@@ -2043,7 +2043,7 @@
         <v>12</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>1</v>
@@ -2057,17 +2057,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27224</t>
+          <t>36953</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>CAMPAGNANO DI ROMA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>SS 2 CASSIA BIS KM30</t>
+          <t>VIA ELSA DE GIORGI</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,39 +2077,39 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>106</v>
+        <v>60</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>92</v>
+        <v>263</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
         <v>11</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>10</v>
@@ -2175,17 +2175,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>36953</t>
+          <t>27224</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CAMPAGNANO DI ROMA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA ELSA DE GIORGI</t>
+          <t>SS 2 CASSIA BIS KM30</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,56 +2195,56 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>266</v>
+        <v>91</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>59331</t>
+          <t>58342</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>MONTALTO DI CASTRO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>S.S. 1 AURELIA SUD KM 107+200</t>
+          <t>VIA GROTTA PERFETTA 546</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,35 +2254,35 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2293,17 +2293,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>58342</t>
+          <t>59331</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MONTALTO DI CASTRO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>VIA GROTTA PERFETTA 546</t>
+          <t>S.S. 1 AURELIA SUD KM 107+200</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2313,39 +2313,39 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         <v>57</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>9</v>
@@ -2388,7 +2388,7 @@
         <v>1</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>13</v>
@@ -2447,7 +2447,7 @@
         <v>6</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>14</v>
@@ -2456,7 +2456,7 @@
         <v>17</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>0</v>
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="H39" s="12" t="n">
         <v>4</v>
@@ -2506,7 +2506,7 @@
         <v>39</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="K39" s="12" t="n">
         <v>15</v>
@@ -2515,7 +2515,7 @@
         <v>6</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>2</v>
@@ -2529,7 +2529,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>27100</t>
+          <t>55307</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA  110 110</t>
+          <t>VIA CASILINA, 930</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2553,31 +2553,31 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G41" s="12" t="n">
         <v>68</v>
@@ -2624,7 +2624,7 @@
         <v>1</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K41" s="12" t="n">
         <v>5</v>
@@ -2633,21 +2633,21 @@
         <v>23</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>55307</t>
+          <t>27100</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA, 930</t>
+          <t>VIA CASILINA  110 110</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2671,31 +2671,31 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>58264</t>
+          <t>36981</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>VIA CIAMPINO KM. 0+370 CAPANNELLE</t>
+          <t>VIA COLLATINA 427, ANG. VIA PETITTI</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Manzo Fabio</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2730,31 +2730,31 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>100</v>
+        <v>195</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>16949</t>
+          <t>58264</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2775,56 +2775,56 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>VIA DI PONTE GALERIA  SNC - VIA DI PONTE GALERIA SNC</t>
+          <t>VIA CIAMPINO KM. 0+370 CAPANNELLE</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Manzo Fabio</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>37</v>
+        <v>93</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>36981</t>
+          <t>07084</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>VIA COLLATINA 427, ANG. VIA PETITTI</t>
+          <t>VIA TUSCOLANA ANG CAVE, 0432</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2848,31 +2848,31 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>195</v>
+        <v>125</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>07084</t>
+          <t>16949</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>VIA TUSCOLANA ANG CAVE, 0432</t>
+          <t>VIA DI PONTE GALERIA  SNC - VIA DI PONTE GALERIA SNC</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2903,35 +2903,35 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>127</v>
+        <v>83</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>6</v>
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>14</v>
@@ -3037,7 +3037,7 @@
         <v>2</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K48" s="12" t="n">
         <v>2</v>
@@ -3053,121 +3053,121 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>58341</t>
+          <t>57171</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>LADISPOLI</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>VIA ARDEATINA</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+          <t>VIA PALO LAZIALE 8</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
         <v>9</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="N49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>57171</t>
+          <t>58341</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>LADISPOLI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>VIA PALO LAZIALE 8</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr"/>
+          <t>VIA ARDEATINA</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
         <v>9</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="J50" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="K50" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L50" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M50" s="12" t="n">
-        <v>63</v>
-      </c>
       <c r="N50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G51" s="12" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
         <v>0</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K51" s="12" t="n">
         <v>2</v>
@@ -3219,14 +3219,14 @@
         <v>1</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N51" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
         <v>0</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K52" s="12" t="n">
         <v>2</v>
@@ -3324,7 +3324,7 @@
         <v>3</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K53" s="12" t="n">
         <v>0</v>
@@ -3370,7 +3370,7 @@
         <v>0</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H54" s="12" t="n">
         <v>0</v>
